--- a/exercisesLifeContingencies/annuities/makeham_comm.xlsx
+++ b/exercisesLifeContingencies/annuities/makeham_comm.xlsx
@@ -456,34 +456,34 @@
         <v>100000</v>
       </c>
       <c r="C2">
-        <v>41.02974113839863</v>
+        <v>22.28393070392576</v>
       </c>
       <c r="D2">
-        <v>0.0004102974113839863</v>
+        <v>0.0002228393070392576</v>
       </c>
       <c r="E2">
-        <v>0.999589702588616</v>
+        <v>0.9997771606929607</v>
       </c>
       <c r="F2">
-        <v>71.66319036298292</v>
+        <v>85.56426560366678</v>
       </c>
       <c r="G2">
         <v>100000</v>
       </c>
       <c r="H2">
-        <v>2388630.327319735</v>
+        <v>2055241.875593928</v>
       </c>
       <c r="I2">
-        <v>50650337.90630667</v>
+        <v>40188846.29433698</v>
       </c>
       <c r="J2">
-        <v>39.45167417153714</v>
+        <v>21.22279114659596</v>
       </c>
       <c r="K2">
-        <v>8129.60279539457</v>
+        <v>2131.339257431903</v>
       </c>
       <c r="L2">
-        <v>440540.4078463971</v>
+        <v>141487.2901493073</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>99958.97025886161</v>
+        <v>99977.71606929608</v>
       </c>
       <c r="C3">
-        <v>43.18377188662431</v>
+        <v>22.31446446393932</v>
       </c>
       <c r="D3">
-        <v>0.0004320149734915457</v>
+        <v>0.0002231943811206172</v>
       </c>
       <c r="E3">
-        <v>0.9995679850265085</v>
+        <v>0.9997768056188794</v>
       </c>
       <c r="F3">
-        <v>70.69240042058567</v>
+        <v>84.5832254906758</v>
       </c>
       <c r="G3">
-        <v>96114.39447967461</v>
+        <v>95216.87244694863</v>
       </c>
       <c r="H3">
-        <v>2288630.327319735</v>
+        <v>1955241.875593928</v>
       </c>
       <c r="I3">
-        <v>48261707.57898694</v>
+        <v>38133604.41874305</v>
       </c>
       <c r="J3">
-        <v>39.9258245993198</v>
+        <v>20.23987706479757</v>
       </c>
       <c r="K3">
-        <v>8090.151121223033</v>
+        <v>2110.116466285307</v>
       </c>
       <c r="L3">
-        <v>432410.8050510027</v>
+        <v>139355.9508918754</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>99915.78648697498</v>
+        <v>99955.40160483214</v>
       </c>
       <c r="C4">
-        <v>45.48688584943878</v>
+        <v>22.34937651317246</v>
       </c>
       <c r="D4">
-        <v>0.0004552522424008387</v>
+        <v>0.0002235934842373943</v>
       </c>
       <c r="E4">
-        <v>0.9995447477575992</v>
+        <v>0.9997764065157626</v>
       </c>
       <c r="F4">
-        <v>69.72273769474938</v>
+        <v>83.60199658375426</v>
       </c>
       <c r="G4">
-        <v>92377.76117508778</v>
+        <v>90662.49578669581</v>
       </c>
       <c r="H4">
-        <v>2192515.93284006</v>
+        <v>1860025.003146979</v>
       </c>
       <c r="I4">
-        <v>45973077.25166719</v>
+        <v>36178362.54314913</v>
       </c>
       <c r="J4">
-        <v>40.43767588743063</v>
+        <v>19.30623173581466</v>
       </c>
       <c r="K4">
-        <v>8050.225296623714</v>
+        <v>2089.876589220509</v>
       </c>
       <c r="L4">
-        <v>424320.6539297796</v>
+        <v>137245.8344255901</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>99870.29960112553</v>
+        <v>99933.05222831896</v>
       </c>
       <c r="C5">
-        <v>47.94928101381507</v>
+        <v>22.38920847730267</v>
       </c>
       <c r="D5">
-        <v>0.0004801155218850939</v>
+        <v>0.0002240420759505035</v>
       </c>
       <c r="E5">
-        <v>0.9995198844781149</v>
+        <v>0.9997759579240495</v>
       </c>
       <c r="F5">
-        <v>68.75426585457552</v>
+        <v>82.62058180425171</v>
       </c>
       <c r="G5">
-        <v>88784.33268477389</v>
+        <v>86325.92785083161</v>
       </c>
       <c r="H5">
-        <v>2100138.171664973</v>
+        <v>1769362.507360283</v>
       </c>
       <c r="I5">
-        <v>43780561.31882714</v>
+        <v>34318337.54000215</v>
       </c>
       <c r="J5">
-        <v>40.98724636747117</v>
+        <v>18.41965722290829</v>
       </c>
       <c r="K5">
-        <v>8009.787620736282</v>
+        <v>2070.570357484694</v>
       </c>
       <c r="L5">
-        <v>416270.4286331558</v>
+        <v>135155.9578363696</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>99822.35032011171</v>
+        <v>99910.66301984167</v>
       </c>
       <c r="C6">
-        <v>50.58183621406519</v>
+        <v>22.43456899188494</v>
       </c>
       <c r="D6">
-        <v>0.0005067185460155832</v>
+        <v>0.0002245462927958908</v>
       </c>
       <c r="E6">
-        <v>0.9994932814539844</v>
+        <v>0.9997754537072041</v>
       </c>
       <c r="F6">
-        <v>67.78705152795786</v>
+        <v>81.63898439283155</v>
       </c>
       <c r="G6">
-        <v>85328.56341206895</v>
+        <v>82196.74972452149</v>
       </c>
       <c r="H6">
-        <v>2011353.838980199</v>
+        <v>1683036.579509452</v>
       </c>
       <c r="I6">
-        <v>41680423.14716216</v>
+        <v>32548975.03264187</v>
       </c>
       <c r="J6">
-        <v>41.57458229400199</v>
+        <v>17.57807183858377</v>
       </c>
       <c r="K6">
-        <v>7968.80037436881</v>
+        <v>2052.150700261786</v>
       </c>
       <c r="L6">
-        <v>408260.6410124195</v>
+        <v>133085.3874788849</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>99771.76848389764</v>
+        <v>99888.22845084978</v>
       </c>
       <c r="C7">
-        <v>53.39615414241699</v>
+        <v>22.48614199029288</v>
       </c>
       <c r="D7">
-        <v>0.0005351829976937283</v>
+        <v>0.0002251130322263872</v>
       </c>
       <c r="E7">
-        <v>0.9994648170023063</v>
+        <v>0.9997748869677736</v>
       </c>
       <c r="F7">
-        <v>66.82116441050402</v>
+        <v>80.65720794300881</v>
       </c>
       <c r="G7">
-        <v>82005.12100623384</v>
+        <v>78265.04071341998</v>
       </c>
       <c r="H7">
-        <v>1926025.27556813</v>
+        <v>1600839.82978493</v>
       </c>
       <c r="I7">
-        <v>39669069.30818196</v>
+        <v>30865938.45313241</v>
       </c>
       <c r="J7">
-        <v>42.19975623687802</v>
+        <v>16.77950536411392</v>
       </c>
       <c r="K7">
-        <v>7927.225792074809</v>
+        <v>2034.572628423202</v>
       </c>
       <c r="L7">
-        <v>400291.8406380507</v>
+        <v>131033.2367786231</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>99718.37232975522</v>
+        <v>99865.7423088595</v>
       </c>
       <c r="C8">
-        <v>56.40460671354154</v>
+        <v>22.54469601619907</v>
       </c>
       <c r="D8">
-        <v>0.0005656390632512442</v>
+        <v>0.0002257500469627916</v>
       </c>
       <c r="E8">
-        <v>0.9994343609367488</v>
+        <v>0.9997742499530372</v>
       </c>
       <c r="F8">
-        <v>65.85667737601911</v>
+        <v>79.67525643809513</v>
       </c>
       <c r="G8">
-        <v>78808.87813437256</v>
+        <v>74521.35450741681</v>
       </c>
       <c r="H8">
-        <v>1844020.154561896</v>
+        <v>1522574.789071511</v>
       </c>
       <c r="I8">
-        <v>37743044.03261384</v>
+        <v>29265098.62334748</v>
       </c>
       <c r="J8">
-        <v>42.86286538827689</v>
+        <v>16.0220945521716</v>
       </c>
       <c r="K8">
-        <v>7885.026035837931</v>
+        <v>2017.793123059088</v>
       </c>
       <c r="L8">
-        <v>392364.6148459759</v>
+        <v>128998.6641501999</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>99661.96772304169</v>
+        <v>99843.1976128433</v>
       </c>
       <c r="C9">
-        <v>59.62038285531604</v>
+        <v>22.61109468680176</v>
       </c>
       <c r="D9">
-        <v>0.0005982260256088834</v>
+        <v>0.0002264660510421512</v>
       </c>
       <c r="E9">
-        <v>0.9994017739743911</v>
+        <v>0.9997735339489578</v>
       </c>
       <c r="F9">
-        <v>64.89366658833069</v>
+        <v>78.69313429188064</v>
       </c>
       <c r="G9">
-        <v>75734.90457150842</v>
+        <v>70956.69648394002</v>
       </c>
       <c r="H9">
-        <v>1765211.276427523</v>
+        <v>1448053.434564094</v>
       </c>
       <c r="I9">
-        <v>35899023.87805194</v>
+        <v>27742523.83427597</v>
       </c>
       <c r="J9">
-        <v>43.56402977084763</v>
+        <v>15.30407890258514</v>
       </c>
       <c r="K9">
-        <v>7842.163170449653</v>
+        <v>2001.771028506917</v>
       </c>
       <c r="L9">
-        <v>384479.588810138</v>
+        <v>126980.8710271408</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>99602.34734018637</v>
+        <v>99820.5865181565</v>
       </c>
       <c r="C10">
-        <v>63.05753879039505</v>
+        <v>22.68630844897002</v>
       </c>
       <c r="D10">
-        <v>0.0006330928986545414</v>
+        <v>0.0002272708390151923</v>
       </c>
       <c r="E10">
-        <v>0.9993669071013455</v>
+        <v>0.9997727291609848</v>
       </c>
       <c r="F10">
-        <v>63.93221161420586</v>
+        <v>77.71084639341203</v>
       </c>
       <c r="G10">
-        <v>72778.45959667956</v>
+        <v>67562.50209627839</v>
       </c>
       <c r="H10">
-        <v>1689476.371856015</v>
+        <v>1377096.738080154</v>
       </c>
       <c r="I10">
-        <v>34133812.60162441</v>
+        <v>26294470.39971188</v>
       </c>
       <c r="J10">
-        <v>44.30339033237912</v>
+        <v>14.62379670227322</v>
       </c>
       <c r="K10">
-        <v>7798.599140678805</v>
+        <v>1986.466949604332</v>
       </c>
       <c r="L10">
-        <v>376637.4256396883</v>
+        <v>124979.0999986339</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>99539.28980139598</v>
+        <v>99797.90020970753</v>
       </c>
       <c r="C11">
-        <v>66.73105086317743</v>
+        <v>22.77142778784285</v>
       </c>
       <c r="D11">
-        <v>0.0006703991056830061</v>
+        <v>0.000228175419923593</v>
       </c>
       <c r="E11">
-        <v>0.999329600894317</v>
+        <v>0.9997718245800764</v>
       </c>
       <c r="F11">
-        <v>62.97239553708098</v>
+        <v>76.72839815625679</v>
       </c>
       <c r="G11">
-        <v>69934.98468339795</v>
+        <v>64330.61629499143</v>
       </c>
       <c r="H11">
-        <v>1616697.912259336</v>
+        <v>1309534.235983875</v>
       </c>
       <c r="I11">
-        <v>32444336.2297684</v>
+        <v>24917373.66163172</v>
       </c>
       <c r="J11">
-        <v>45.08110691125453</v>
+        <v>13.97968132100305</v>
       </c>
       <c r="K11">
-        <v>7754.295750346427</v>
+        <v>1971.843152902059</v>
       </c>
       <c r="L11">
-        <v>368838.8264990096</v>
+        <v>122992.6330490295</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>99472.5587505328</v>
+        <v>99775.12878191969</v>
       </c>
       <c r="C12">
-        <v>70.65687095394316</v>
+        <v>22.86767806680746</v>
       </c>
       <c r="D12">
-        <v>0.0007103152049314776</v>
+        <v>0.0002291921678877484</v>
       </c>
       <c r="E12">
-        <v>0.9992896847950685</v>
+        <v>0.9997708078321123</v>
       </c>
       <c r="F12">
-        <v>62.01430507129317</v>
+        <v>75.745795572679</v>
       </c>
       <c r="G12">
-        <v>67200.09647327907</v>
+        <v>61253.27393295654</v>
       </c>
       <c r="H12">
-        <v>1546762.927575937</v>
+        <v>1245203.619688884</v>
       </c>
       <c r="I12">
-        <v>30827638.31750906</v>
+        <v>23607839.42564785</v>
       </c>
       <c r="J12">
-        <v>45.89735605560797</v>
+        <v>13.3702577551585</v>
       </c>
       <c r="K12">
-        <v>7709.214643435173</v>
+        <v>1957.863471581055</v>
       </c>
       <c r="L12">
-        <v>361084.5307486631</v>
+        <v>121020.7898961275</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -871,37 +871,37 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>99401.90187957886</v>
+        <v>99752.26110385288</v>
       </c>
       <c r="C13">
-        <v>74.85198450612164</v>
+        <v>22.97643619998853</v>
       </c>
       <c r="D13">
-        <v>0.0007530236654506028</v>
+        <v>0.0002303349913649333</v>
       </c>
       <c r="E13">
-        <v>0.9992469763345494</v>
+        <v>0.9997696650086351</v>
       </c>
       <c r="F13">
-        <v>61.0580306764683</v>
+        <v>74.76304527318699</v>
       </c>
       <c r="G13">
-        <v>64569.58002209734</v>
+        <v>58323.08110696536</v>
       </c>
       <c r="H13">
-        <v>1479562.831102659</v>
+        <v>1183950.345755927</v>
       </c>
       <c r="I13">
-        <v>29280875.38993312</v>
+        <v>22362635.80595896</v>
       </c>
       <c r="J13">
-        <v>46.75232867773631</v>
+        <v>12.79413941252302</v>
       </c>
       <c r="K13">
-        <v>7663.317287379565</v>
+        <v>1944.493213825897</v>
       </c>
       <c r="L13">
-        <v>353375.3161052279</v>
+        <v>119062.9264245464</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -909,37 +909,37 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>99327.04989507273</v>
+        <v>99729.2846676529</v>
       </c>
       <c r="C14">
-        <v>79.33447117322143</v>
+        <v>23.09924938315849</v>
       </c>
       <c r="D14">
-        <v>0.0007987196967697008</v>
+        <v>0.0002316195233941221</v>
       </c>
       <c r="E14">
-        <v>0.9992012803032303</v>
+        <v>0.9997683804766059</v>
       </c>
       <c r="F14">
-        <v>60.10366667168516</v>
+        <v>73.78015459195352</v>
       </c>
       <c r="G14">
-        <v>62039.38230795432</v>
+        <v>55532.99739103068</v>
       </c>
       <c r="H14">
-        <v>1414993.251080561</v>
+        <v>1125627.264648962</v>
       </c>
       <c r="I14">
-        <v>27801312.55883047</v>
+        <v>21178685.46020303</v>
       </c>
       <c r="J14">
-        <v>47.64622752383539</v>
+        <v>12.25002513176909</v>
       </c>
       <c r="K14">
-        <v>7616.564958701827</v>
+        <v>1931.699074413374</v>
       </c>
       <c r="L14">
-        <v>345711.9988178483</v>
+        <v>117118.4332107205</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -947,37 +947,37 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>99247.71542389951</v>
+        <v>99706.18541826974</v>
       </c>
       <c r="C15">
-        <v>84.12356806795022</v>
+        <v>23.23785613606873</v>
       </c>
       <c r="D15">
-        <v>0.000847612136044118</v>
+        <v>0.0002330633354248324</v>
       </c>
       <c r="E15">
-        <v>0.9991523878639559</v>
+        <v>0.9997669366645752</v>
       </c>
       <c r="F15">
-        <v>59.15131134899774</v>
+        <v>72.79713163864982</v>
       </c>
       <c r="G15">
-        <v>59605.605991663</v>
+        <v>52876.31891870697</v>
       </c>
       <c r="H15">
-        <v>1352953.868772607</v>
+        <v>1070094.267257931</v>
       </c>
       <c r="I15">
-        <v>26386319.3077499</v>
+        <v>20053058.19555407</v>
       </c>
       <c r="J15">
-        <v>48.57926443730533</v>
+        <v>11.73669643064858</v>
       </c>
       <c r="K15">
-        <v>7568.918731177992</v>
+        <v>1919.449049281605</v>
       </c>
       <c r="L15">
-        <v>338095.4338591465</v>
+        <v>115186.7341363072</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -985,37 +985,37 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>99163.59185583156</v>
+        <v>99682.94756213368</v>
       </c>
       <c r="C16">
-        <v>89.23973556833595</v>
+        <v>23.39420994107155</v>
       </c>
       <c r="D16">
-        <v>0.0008999243966281156</v>
+        <v>0.0002346861776583165</v>
       </c>
       <c r="E16">
-        <v>0.9991000756033719</v>
+        <v>0.9997653138223417</v>
       </c>
       <c r="F16">
-        <v>58.20106708585845</v>
+        <v>71.81398537727971</v>
       </c>
       <c r="G16">
-        <v>57264.50341985404</v>
+        <v>50346.66227376646</v>
       </c>
       <c r="H16">
-        <v>1293348.262780944</v>
+        <v>1017217.948339224</v>
       </c>
       <c r="I16">
-        <v>25033365.4389773</v>
+        <v>18982963.92829614</v>
       </c>
       <c r="J16">
-        <v>49.55165739261616</v>
+        <v>11.25301497798516</v>
       </c>
       <c r="K16">
-        <v>7520.339466740687</v>
+        <v>1907.712352850956</v>
       </c>
       <c r="L16">
-        <v>330526.5151279685</v>
+        <v>113267.2850870255</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1023,37 +1023,37 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>99074.35212026323</v>
+        <v>99659.5533521926</v>
       </c>
       <c r="C17">
-        <v>94.70472560042595</v>
+        <v>23.57050579692938</v>
       </c>
       <c r="D17">
-        <v>0.0009558954822683763</v>
+        <v>0.0002365102491843629</v>
       </c>
       <c r="E17">
-        <v>0.9990441045177316</v>
+        <v>0.9997634897508156</v>
       </c>
       <c r="F17">
-        <v>57.25304045594421</v>
+        <v>70.83072571264681</v>
       </c>
       <c r="G17">
-        <v>55012.47086169781</v>
+        <v>47937.94915051388</v>
       </c>
       <c r="H17">
-        <v>1236083.75936109</v>
+        <v>966871.2860654577</v>
       </c>
       <c r="I17">
-        <v>23740017.17619635</v>
+        <v>17965745.97995692</v>
       </c>
       <c r="J17">
-        <v>50.56362727415155</v>
+        <v>10.79792028473843</v>
       </c>
       <c r="K17">
-        <v>7470.787809348071</v>
+        <v>1896.459337872971</v>
       </c>
       <c r="L17">
-        <v>323006.1756612278</v>
+        <v>111359.5727341746</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1061,37 +1061,37 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>98979.6473946628</v>
+        <v>99635.98284639567</v>
       </c>
       <c r="C18">
-        <v>100.5416522778493</v>
+        <v>23.76921004595136</v>
       </c>
       <c r="D18">
-        <v>0.001015781071405097</v>
+        <v>0.000238560501607088</v>
       </c>
       <c r="E18">
-        <v>0.9989842189285949</v>
+        <v>0.9997614394983929</v>
       </c>
       <c r="F18">
-        <v>56.30734233784462</v>
+        <v>69.84736358513778</v>
       </c>
       <c r="G18">
-        <v>52846.04297051219</v>
+        <v>45644.39174687133</v>
       </c>
       <c r="H18">
-        <v>1181071.288499392</v>
+        <v>918933.3369149438</v>
       </c>
       <c r="I18">
-        <v>22503933.41683526</v>
+        <v>16998874.69389146</v>
       </c>
       <c r="J18">
-        <v>51.61539437317951</v>
+        <v>10.37042761017529</v>
       </c>
       <c r="K18">
-        <v>7420.224182073919</v>
+        <v>1885.661417588233</v>
       </c>
       <c r="L18">
-        <v>315535.3878518797</v>
+        <v>109463.1133963016</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1099,37 +1099,37 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>98879.10574238494</v>
+        <v>99612.21363634971</v>
       </c>
       <c r="C19">
-        <v>106.7750647299199</v>
+        <v>23.99309387628278</v>
       </c>
       <c r="D19">
-        <v>0.001079854676357073</v>
+        <v>0.0002408649803112839</v>
       </c>
       <c r="E19">
-        <v>0.9989201453236429</v>
+        <v>0.9997591350196887</v>
       </c>
       <c r="F19">
-        <v>55.36408802102768</v>
+        <v>68.86391107455717</v>
       </c>
       <c r="G19">
-        <v>50761.88746188854</v>
+        <v>43460.47885512443</v>
       </c>
       <c r="H19">
-        <v>1128225.24552888</v>
+        <v>873288.9451680725</v>
       </c>
       <c r="I19">
-        <v>21322862.12833587</v>
+        <v>16079941.35697652</v>
       </c>
       <c r="J19">
-        <v>52.7071745734921</v>
+        <v>9.969626079770013</v>
       </c>
       <c r="K19">
-        <v>7368.60878770074</v>
+        <v>1875.290989978057</v>
       </c>
       <c r="L19">
-        <v>308115.1636698059</v>
+        <v>107577.4519787134</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1137,37 +1137,37 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>98772.33067765502</v>
+        <v>99588.22054247343</v>
       </c>
       <c r="C20">
-        <v>113.4310218939008</v>
+        <v>24.24527094990752</v>
       </c>
       <c r="D20">
-        <v>0.001148408882484353</v>
+        <v>0.000243455208034038</v>
       </c>
       <c r="E20">
-        <v>0.9988515911175156</v>
+        <v>0.999756544791966</v>
       </c>
       <c r="F20">
-        <v>54.42339730845264</v>
+        <v>67.88038151380417</v>
       </c>
       <c r="G20">
-        <v>48756.80000031932</v>
+        <v>41380.96261689586</v>
       </c>
       <c r="H20">
-        <v>1077463.358066991</v>
+        <v>829828.466312948</v>
       </c>
       <c r="I20">
-        <v>20194636.88280699</v>
+        <v>15206652.41180845</v>
       </c>
       <c r="J20">
-        <v>53.83917519411521</v>
+        <v>9.594677011947743</v>
       </c>
       <c r="K20">
-        <v>7315.901613127248</v>
+        <v>1865.321363898287</v>
       </c>
       <c r="L20">
-        <v>300746.5548821051</v>
+        <v>105702.1609887353</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1175,37 +1175,37 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>98658.89965576111</v>
+        <v>99563.97527152352</v>
       </c>
       <c r="C21">
-        <v>120.5371689818844</v>
+        <v>24.52923966152514</v>
       </c>
       <c r="D21">
-        <v>0.00122175667276303</v>
+        <v>0.0002463666159836508</v>
       </c>
       <c r="E21">
-        <v>0.998778243327237</v>
+        <v>0.9997536333840163</v>
       </c>
       <c r="F21">
-        <v>53.4853946151531</v>
+        <v>66.89678961324029</v>
       </c>
       <c r="G21">
-        <v>46827.69928665138</v>
+        <v>39400.84591050792</v>
       </c>
       <c r="H21">
-        <v>1028706.558066672</v>
+        <v>788447.5036960521</v>
       </c>
       <c r="I21">
-        <v>19117173.52474</v>
+        <v>14376823.9454955</v>
       </c>
       <c r="J21">
-        <v>55.01159045539126</v>
+        <v>9.244812451300099</v>
       </c>
       <c r="K21">
-        <v>7262.062437933133</v>
+        <v>1855.72668688634</v>
       </c>
       <c r="L21">
-        <v>293430.6532689779</v>
+        <v>103836.839624837</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1213,37 +1213,37 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>98538.36248677922</v>
+        <v>99539.446031862</v>
       </c>
       <c r="C22">
-        <v>128.1228152552156</v>
+        <v>24.84893059472741</v>
       </c>
       <c r="D22">
-        <v>0.00130023284355274</v>
+        <v>0.000249639028398585</v>
       </c>
       <c r="E22">
-        <v>0.9986997671564473</v>
+        <v>0.9997503609716014</v>
       </c>
       <c r="F22">
-        <v>52.55020906206617</v>
+        <v>65.91315159665596</v>
       </c>
       <c r="G22">
-        <v>44971.62233901709</v>
+        <v>37515.37034041338</v>
       </c>
       <c r="H22">
-        <v>981878.8587800206</v>
+        <v>749046.6577855442</v>
       </c>
       <c r="I22">
-        <v>18088466.96667333</v>
+        <v>13588376.44179945</v>
       </c>
       <c r="J22">
-        <v>56.22459653176932</v>
+        <v>8.919333906470371</v>
       </c>
       <c r="K22">
-        <v>7207.050847477741</v>
+        <v>1846.48187443504</v>
       </c>
       <c r="L22">
-        <v>286168.5908310447</v>
+        <v>101981.1129379507</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1251,37 +1251,37 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>98410.239671524</v>
+        <v>99514.59710126727</v>
       </c>
       <c r="C23">
-        <v>136.2190126516928</v>
+        <v>25.20875981004588</v>
       </c>
       <c r="D23">
-        <v>0.001384195517726283</v>
+        <v>0.0002533172071670364</v>
       </c>
       <c r="E23">
-        <v>0.9986158044822737</v>
+        <v>0.999746682792833</v>
       </c>
       <c r="F23">
-        <v>51.61797456433415</v>
+        <v>64.92948534980732</v>
       </c>
       <c r="G23">
-        <v>43185.71996021542</v>
+        <v>35720.00479982056</v>
       </c>
       <c r="H23">
-        <v>936907.2364410036</v>
+        <v>711531.2874451309</v>
       </c>
       <c r="I23">
-        <v>17106588.10789331</v>
+        <v>12839329.7840139</v>
       </c>
       <c r="J23">
-        <v>57.47834615260833</v>
+        <v>8.617611291317791</v>
       </c>
       <c r="K23">
-        <v>7150.826250945971</v>
+        <v>1837.562540528569</v>
       </c>
       <c r="L23">
-        <v>278961.539983567</v>
+        <v>100134.6310635157</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1289,37 +1289,37 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>98274.02065887231</v>
+        <v>99489.38834145722</v>
       </c>
       <c r="C24">
-        <v>144.8586347068926</v>
+        <v>25.61368867592734</v>
       </c>
       <c r="D24">
-        <v>0.001474027761718677</v>
+        <v>0.0002574514639492875</v>
       </c>
       <c r="E24">
-        <v>0.9985259722382813</v>
+        <v>0.9997425485360507</v>
       </c>
       <c r="F24">
-        <v>50.68882991325774</v>
+        <v>63.94581058255771</v>
       </c>
       <c r="G24">
-        <v>41467.25238482375</v>
+        <v>34010.43457901398</v>
       </c>
       <c r="H24">
-        <v>893721.5164807881</v>
+        <v>675811.2826453103</v>
       </c>
       <c r="I24">
-        <v>16169680.87145231</v>
+        <v>12127798.49656877</v>
       </c>
       <c r="J24">
-        <v>58.77296270906271</v>
+        <v>8.339082068493923</v>
       </c>
       <c r="K24">
-        <v>7093.347904793363</v>
+        <v>1828.944929237251</v>
       </c>
       <c r="L24">
-        <v>271810.713732621</v>
+        <v>98297.0685229871</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1327,37 +1327,37 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>98129.16202416542</v>
+        <v>99463.77465278129</v>
       </c>
       <c r="C25">
-        <v>154.0764550935945</v>
+        <v>26.06929103873174</v>
       </c>
       <c r="D25">
-        <v>0.001570139313486152</v>
+        <v>0.0002620983481648187</v>
       </c>
       <c r="E25">
-        <v>0.9984298606865138</v>
+        <v>0.9997379016518352</v>
       </c>
       <c r="F25">
-        <v>49.76291885102917</v>
+        <v>62.96214900572461</v>
       </c>
       <c r="G25">
-        <v>39813.58509962146</v>
+        <v>32382.55099318291</v>
       </c>
       <c r="H25">
-        <v>852254.2640959644</v>
+        <v>641800.8480662962</v>
       </c>
       <c r="I25">
-        <v>15275959.35497152</v>
+        <v>11451987.21392346</v>
       </c>
       <c r="J25">
-        <v>60.10853382282897</v>
+        <v>8.083250594929762</v>
       </c>
       <c r="K25">
-        <v>7034.5749420843</v>
+        <v>1820.605847168757</v>
       </c>
       <c r="L25">
-        <v>264717.3658278277</v>
+        <v>96468.12359374984</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1365,37 +1365,37 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>97975.08556907182</v>
+        <v>99437.70536174256</v>
       </c>
       <c r="C26">
-        <v>163.9092249666821</v>
+        <v>26.58182862274045</v>
       </c>
       <c r="D26">
-        <v>0.001672968428806598</v>
+        <v>0.0002673214202403296</v>
       </c>
       <c r="E26">
-        <v>0.9983270315711934</v>
+        <v>0.9997326785797597</v>
       </c>
       <c r="F26">
-        <v>48.84039013732653</v>
+        <v>61.97852452379806</v>
       </c>
       <c r="G26">
-        <v>38222.1848311978</v>
+        <v>30832.44150481737</v>
       </c>
       <c r="H26">
-        <v>812440.6789963429</v>
+        <v>609418.2970731134</v>
       </c>
       <c r="I26">
-        <v>14423705.09087555</v>
+        <v>10810186.36585717</v>
       </c>
       <c r="J26">
-        <v>61.48510432942729</v>
+        <v>7.849687669090152</v>
       </c>
       <c r="K26">
-        <v>6974.466408261471</v>
+        <v>1812.522596573828</v>
       </c>
       <c r="L26">
-        <v>257682.7908857434</v>
+        <v>94647.51774658108</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1403,37 +1403,37 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>97811.17634410513</v>
+        <v>99411.12353311981</v>
       </c>
       <c r="C27">
-        <v>174.3957481454433</v>
+        <v>27.15833565723852</v>
       </c>
       <c r="D27">
-        <v>0.001782983853827802</v>
+        <v>0.0002731921206804433</v>
       </c>
       <c r="E27">
-        <v>0.9982170161461722</v>
+        <v>0.9997268078793196</v>
       </c>
       <c r="F27">
-        <v>47.9213976068014</v>
+        <v>60.99496344476375</v>
       </c>
       <c r="G27">
-        <v>36690.61569489923</v>
+        <v>29356.38031691887</v>
       </c>
       <c r="H27">
-        <v>774218.4941651451</v>
+        <v>578585.855568296</v>
       </c>
       <c r="I27">
-        <v>13611264.41187921</v>
+        <v>10200768.06878405</v>
       </c>
       <c r="J27">
-        <v>62.90266862596755</v>
+        <v>7.638030280267325</v>
       </c>
       <c r="K27">
-        <v>6912.981303932044</v>
+        <v>1804.672908904737</v>
       </c>
       <c r="L27">
-        <v>250708.3244774819</v>
+        <v>92834.99515000726</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1441,37 +1441,37 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>97636.78059595969</v>
+        <v>99383.96519746257</v>
       </c>
       <c r="C28">
-        <v>185.5769529876072</v>
+        <v>27.80671384487818</v>
       </c>
       <c r="D28">
-        <v>0.001900686932269524</v>
+        <v>0.0002797907468234939</v>
       </c>
       <c r="E28">
-        <v>0.9980993130677305</v>
+        <v>0.9997202092531765</v>
       </c>
       <c r="F28">
-        <v>47.00610021644565</v>
+        <v>60.01149470832866</v>
       </c>
       <c r="G28">
-        <v>35216.53549954636</v>
+        <v>27950.81941440437</v>
       </c>
       <c r="H28">
-        <v>737527.8784702459</v>
+        <v>549229.4752513771</v>
       </c>
       <c r="I28">
-        <v>12837045.91771407</v>
+        <v>9622182.213215755</v>
       </c>
       <c r="J28">
-        <v>64.36116233057075</v>
+        <v>7.447981560271249</v>
       </c>
       <c r="K28">
-        <v>6850.078635306078</v>
+        <v>1797.03487862447</v>
       </c>
       <c r="L28">
-        <v>243795.3431735499</v>
+        <v>91030.32224110252</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1479,37 +1479,37 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>97451.20364297208</v>
+        <v>99356.15848361769</v>
       </c>
       <c r="C29">
-        <v>197.4959596073467</v>
+        <v>28.53583891695504</v>
       </c>
       <c r="D29">
-        <v>0.002026613856211612</v>
+        <v>0.0002872075506186178</v>
       </c>
       <c r="E29">
-        <v>0.9979733861437884</v>
+        <v>0.9997127924493814</v>
       </c>
       <c r="F29">
-        <v>46.09466208177801</v>
+        <v>59.02815013391166</v>
       </c>
       <c r="G29">
-        <v>33797.69220261785</v>
+        <v>26612.38003215818</v>
       </c>
       <c r="H29">
-        <v>702311.3429706995</v>
+        <v>521278.6558369728</v>
       </c>
       <c r="I29">
-        <v>12099518.03924382</v>
+        <v>9072952.737964377</v>
       </c>
       <c r="J29">
-        <v>65.86045319788509</v>
+        <v>7.279310938255203</v>
       </c>
       <c r="K29">
-        <v>6785.717472975507</v>
+        <v>1789.586897064199</v>
       </c>
       <c r="L29">
-        <v>236945.2645382438</v>
+        <v>89233.28736247805</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1517,37 +1517,37 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>97253.70768336473</v>
+        <v>99327.62264470074</v>
       </c>
       <c r="C30">
-        <v>210.1981408599101</v>
+        <v>29.35568016571148</v>
       </c>
       <c r="D30">
-        <v>0.002161338069950669</v>
+        <v>0.0002955439724025011</v>
       </c>
       <c r="E30">
-        <v>0.9978386619300493</v>
+        <v>0.9997044560275975</v>
       </c>
       <c r="F30">
-        <v>45.18725250074827</v>
+        <v>58.04496468982128</v>
       </c>
       <c r="G30">
-        <v>32431.92051085774</v>
+        <v>25337.84452921239</v>
       </c>
       <c r="H30">
-        <v>668513.6507680815</v>
+        <v>494666.2758048146</v>
       </c>
       <c r="I30">
-        <v>11397206.69627312</v>
+        <v>8551674.082127405</v>
       </c>
       <c r="J30">
-        <v>67.40033123243343</v>
+        <v>7.131854499314675</v>
       </c>
       <c r="K30">
-        <v>6719.857019777621</v>
+        <v>1782.307586125944</v>
       </c>
       <c r="L30">
-        <v>230159.5470652683</v>
+        <v>87443.70046541386</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1555,37 +1555,37 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>97043.50954250482</v>
+        <v>99298.26696453503</v>
       </c>
       <c r="C31">
-        <v>223.7311752572228</v>
+        <v>30.27743450465336</v>
       </c>
       <c r="D31">
-        <v>0.002305472836998224</v>
+        <v>0.0003049140275073192</v>
       </c>
       <c r="E31">
-        <v>0.9976945271630018</v>
+        <v>0.9996950859724927</v>
       </c>
       <c r="F31">
-        <v>44.28404596421716</v>
+        <v>57.06197678509969</v>
       </c>
       <c r="G31">
-        <v>31117.13862151539</v>
+        <v>24124.14864951248</v>
       </c>
       <c r="H31">
-        <v>636081.7302572238</v>
+        <v>469328.4312756023</v>
       </c>
       <c r="I31">
-        <v>10728693.04550504</v>
+        <v>8057007.80632259</v>
       </c>
       <c r="J31">
-        <v>68.98049793943468</v>
+        <v>7.005515547531529</v>
       </c>
       <c r="K31">
-        <v>6652.456688545188</v>
+        <v>1775.175731626629</v>
       </c>
       <c r="L31">
-        <v>223439.6900454907</v>
+        <v>85661.39287928792</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1593,37 +1593,37 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>96819.77836724759</v>
+        <v>99267.98953003038</v>
       </c>
       <c r="C32">
-        <v>238.1450896860658</v>
+        <v>31.3136767854815</v>
       </c>
       <c r="D32">
-        <v>0.002459673980896304</v>
+        <v>0.0003154458646108527</v>
       </c>
       <c r="E32">
-        <v>0.9975403260191037</v>
+        <v>0.9996845541353891</v>
       </c>
       <c r="F32">
-        <v>43.38522215183383</v>
+        <v>56.07922858556097</v>
       </c>
       <c r="G32">
-        <v>29851.34509967151</v>
+        <v>22968.37415065483</v>
       </c>
       <c r="H32">
-        <v>604964.5916357085</v>
+        <v>445204.2826260898</v>
       </c>
       <c r="I32">
-        <v>10092611.31524781</v>
+        <v>7587679.375046989</v>
       </c>
       <c r="J32">
-        <v>70.60055465040232</v>
+        <v>6.90026537396083</v>
       </c>
       <c r="K32">
-        <v>6583.476190605754</v>
+        <v>1768.170216079097</v>
       </c>
       <c r="L32">
-        <v>216787.2333569455</v>
+        <v>83886.21714766129</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1631,37 +1631,37 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>96581.63327756153</v>
+        <v>99236.67585324489</v>
       </c>
       <c r="C33">
-        <v>253.4922894734195</v>
+        <v>32.47852829574072</v>
       </c>
       <c r="D33">
-        <v>0.002624642811174249</v>
+        <v>0.0003272835170715638</v>
       </c>
       <c r="E33">
-        <v>0.9973753571888258</v>
+        <v>0.9996727164829284</v>
       </c>
       <c r="F33">
-        <v>42.49096591210142</v>
+        <v>55.09676635559358</v>
       </c>
       <c r="G33">
-        <v>28632.61588734144</v>
+        <v>21867.74178286874</v>
       </c>
       <c r="H33">
-        <v>575113.246536037</v>
+        <v>422235.9084754349</v>
       </c>
       <c r="I33">
-        <v>9487646.723612104</v>
+        <v>7142475.092420898</v>
       </c>
       <c r="J33">
-        <v>72.25998985944643</v>
+        <v>6.816144229628636</v>
       </c>
       <c r="K33">
-        <v>6512.875635955351</v>
+        <v>1761.269950705137</v>
       </c>
       <c r="L33">
-        <v>210203.7571663398</v>
+        <v>82118.04693158218</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1669,37 +1669,37 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>96328.14098808811</v>
+        <v>99204.19732494914</v>
       </c>
       <c r="C34">
-        <v>269.8275729766773</v>
+        <v>33.78784557659677</v>
       </c>
       <c r="D34">
-        <v>0.002801129246437384</v>
+        <v>0.0003405888711132121</v>
       </c>
       <c r="E34">
-        <v>0.9971988707535626</v>
+        <v>0.9996594111288868</v>
       </c>
       <c r="F34">
-        <v>41.60146722539445</v>
+        <v>54.11464082732714</v>
       </c>
       <c r="G34">
-        <v>27459.10144027655</v>
+        <v>20819.60460135964</v>
       </c>
       <c r="H34">
-        <v>546480.6306486955</v>
+        <v>400368.1666925661</v>
       </c>
       <c r="I34">
-        <v>8912533.477076069</v>
+        <v>6720239.183945464</v>
       </c>
       <c r="J34">
-        <v>73.9581655050476</v>
+        <v>6.75326250304811</v>
       </c>
       <c r="K34">
-        <v>6440.615646095905</v>
+        <v>1754.453806475508</v>
       </c>
       <c r="L34">
-        <v>203690.8815303844</v>
+        <v>80356.77698087705</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1707,37 +1707,37 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>96058.31341511144</v>
+        <v>99170.40947937254</v>
       </c>
       <c r="C35">
-        <v>287.2081274684362</v>
+        <v>35.259431935956</v>
       </c>
       <c r="D35">
-        <v>0.00298993514728163</v>
+        <v>0.000355543877665343</v>
       </c>
       <c r="E35">
-        <v>0.9970100648527184</v>
+        <v>0.9996444561223347</v>
       </c>
       <c r="F35">
-        <v>40.7169211486721</v>
+        <v>53.13290759878074</v>
       </c>
       <c r="G35">
-        <v>26329.02398860702</v>
+        <v>19821.4415959347</v>
       </c>
       <c r="H35">
-        <v>519021.529208419</v>
+        <v>379548.5620912065</v>
       </c>
       <c r="I35">
-        <v>8366052.846427373</v>
+        <v>6319871.017252898</v>
       </c>
       <c r="J35">
-        <v>75.69430213188201</v>
+        <v>6.711802100891188</v>
       </c>
       <c r="K35">
-        <v>6366.657480590858</v>
+        <v>1747.70054397246</v>
       </c>
       <c r="L35">
-        <v>197250.2658842885</v>
+        <v>78602.32317440154</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1745,37 +1745,37 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>95771.105287643</v>
+        <v>99135.15004743657</v>
       </c>
       <c r="C36">
-        <v>305.6935026325128</v>
+        <v>36.91327428958848</v>
       </c>
       <c r="D36">
-        <v>0.003191917872456207</v>
+        <v>0.0003723530379681206</v>
       </c>
       <c r="E36">
-        <v>0.9968080821275438</v>
+        <v>0.9996276469620319</v>
       </c>
       <c r="F36">
-        <v>39.83752774061823</v>
+        <v>52.15162756260975</v>
       </c>
       <c r="G36">
-        <v>25240.67491768255</v>
+        <v>18870.85162259882</v>
       </c>
       <c r="H36">
-        <v>492692.5052198119</v>
+        <v>359727.1204952718</v>
       </c>
       <c r="I36">
-        <v>7847031.317218955</v>
+        <v>5940322.455161691</v>
       </c>
       <c r="J36">
-        <v>77.46746286789234</v>
+        <v>6.692018029257436</v>
       </c>
       <c r="K36">
-        <v>6290.963178458975</v>
+        <v>1740.988741871569</v>
       </c>
       <c r="L36">
-        <v>190883.6084036976</v>
+        <v>76854.62263042908</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1783,37 +1783,37 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>95465.4117850105</v>
+        <v>99098.23677314699</v>
       </c>
       <c r="C37">
-        <v>325.3455574876707</v>
+        <v>38.77180824259952</v>
       </c>
       <c r="D37">
-        <v>0.003407994072453735</v>
+        <v>0.0003912461967547909</v>
       </c>
       <c r="E37">
-        <v>0.9965920059275463</v>
+        <v>0.9996087538032452</v>
       </c>
       <c r="F37">
-        <v>38.96349196593381</v>
+        <v>51.17086736704832</v>
       </c>
       <c r="G37">
-        <v>24192.41226567302</v>
+        <v>17965.54762254105</v>
       </c>
       <c r="H37">
-        <v>467451.8303021294</v>
+        <v>340856.268872673</v>
       </c>
       <c r="I37">
-        <v>7354338.811999143</v>
+        <v>5580595.33466642</v>
       </c>
       <c r="J37">
-        <v>79.27653615362566</v>
+        <v>6.694240171367866</v>
       </c>
       <c r="K37">
-        <v>6213.495715591083</v>
+        <v>1734.296723842311</v>
       </c>
       <c r="L37">
-        <v>184592.6452252386</v>
+        <v>75113.63388855751</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1821,37 +1821,37 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>95140.06622752282</v>
+        <v>99059.46496490439</v>
       </c>
       <c r="C38">
-        <v>346.2283760065334</v>
+        <v>40.86021462610606</v>
       </c>
       <c r="D38">
-        <v>0.003639143735495676</v>
+        <v>0.000412481680984067</v>
       </c>
       <c r="E38">
-        <v>0.9963608562645043</v>
+        <v>0.9995875183190159</v>
       </c>
       <c r="F38">
-        <v>38.09502357751219</v>
+        <v>50.19069991059919</v>
       </c>
       <c r="G38">
-        <v>23182.65833468582</v>
+        <v>17103.35111462963</v>
       </c>
       <c r="H38">
-        <v>443259.4180364563</v>
+        <v>322890.721250132</v>
       </c>
       <c r="I38">
-        <v>6886886.981697014</v>
+        <v>5239739.065793746</v>
       </c>
       <c r="J38">
-        <v>81.12021716423894</v>
+        <v>6.718875255450614</v>
       </c>
       <c r="K38">
-        <v>6134.219179437458</v>
+        <v>1727.602483670943</v>
       </c>
       <c r="L38">
-        <v>178379.1495096476</v>
+        <v>73379.33716471519</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1859,37 +1859,37 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>94793.83785151629</v>
+        <v>99018.60475027827</v>
       </c>
       <c r="C39">
-        <v>368.4081460968807</v>
+        <v>43.20675102869054</v>
       </c>
       <c r="D39">
-        <v>0.003886414501688917</v>
+        <v>0.0004363498267588861</v>
       </c>
       <c r="E39">
-        <v>0.9961135854983111</v>
+        <v>0.9995636501732411</v>
       </c>
       <c r="F39">
-        <v>37.23233697524125</v>
+        <v>49.2112048719485</v>
       </c>
       <c r="G39">
-        <v>22209.89741234135</v>
+        <v>16282.18694820134</v>
       </c>
       <c r="H39">
-        <v>420076.7597017704</v>
+        <v>305787.3701355023</v>
       </c>
       <c r="I39">
-        <v>6443627.563660556</v>
+        <v>4916848.344543614</v>
       </c>
       <c r="J39">
-        <v>82.99698786956402</v>
+        <v>6.766409003908047</v>
       </c>
       <c r="K39">
-        <v>6053.098962273218</v>
+        <v>1720.883608415493</v>
       </c>
       <c r="L39">
-        <v>172244.9303302101</v>
+        <v>71651.73468104425</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1897,37 +1897,37 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>94425.42970541942</v>
+        <v>98975.39799924959</v>
       </c>
       <c r="C40">
-        <v>391.952995961472</v>
+        <v>45.84312220818751</v>
       </c>
       <c r="D40">
-        <v>0.004150926261964116</v>
+        <v>0.0004631769422996923</v>
       </c>
       <c r="E40">
-        <v>0.9958490737380359</v>
+        <v>0.9995368230577003</v>
       </c>
       <c r="F40">
-        <v>36.37565104020311</v>
+        <v>48.23246927647482</v>
       </c>
       <c r="G40">
-        <v>21272.6736009202</v>
+        <v>15500.07830356879</v>
       </c>
       <c r="H40">
-        <v>397866.8622894291</v>
+        <v>289505.183187301</v>
       </c>
       <c r="I40">
-        <v>6023550.803958786</v>
+        <v>4611060.974408112</v>
       </c>
       <c r="J40">
-        <v>84.90509568485616</v>
+        <v>6.837408451478852</v>
       </c>
       <c r="K40">
-        <v>5970.101974403655</v>
+        <v>1714.117199411585</v>
       </c>
       <c r="L40">
-        <v>166191.8313679369</v>
+        <v>69930.85107262876</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1935,37 +1935,37 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>94033.47670945794</v>
+        <v>98929.5548770414</v>
       </c>
       <c r="C41">
-        <v>416.9327811511048</v>
+        <v>48.80489363396037</v>
       </c>
       <c r="D41">
-        <v>0.0044338760592606</v>
+        <v>0.0004933297607031539</v>
       </c>
       <c r="E41">
-        <v>0.9955661239407394</v>
+        <v>0.9995066702392968</v>
       </c>
       <c r="F41">
-        <v>35.52518894307917</v>
+        <v>47.25458810057203</v>
       </c>
       <c r="G41">
-        <v>20369.5887513538</v>
+        <v>14755.14192828071</v>
       </c>
       <c r="H41">
-        <v>376594.1886885089</v>
+        <v>274005.1048837322</v>
       </c>
       <c r="I41">
-        <v>5625683.941669357</v>
+        <v>4321555.79122081</v>
       </c>
       <c r="J41">
-        <v>86.84253067462654</v>
+        <v>6.932524415828374</v>
       </c>
       <c r="K41">
-        <v>5885.196878718798</v>
+        <v>1707.279790960106</v>
       </c>
       <c r="L41">
-        <v>160221.7293935333</v>
+        <v>68216.73387321718</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -1973,37 +1973,37 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>93616.54392830684</v>
+        <v>98880.74998340744</v>
       </c>
       <c r="C42">
-        <v>443.4188148763046</v>
+        <v>52.13195279015003</v>
       </c>
       <c r="D42">
-        <v>0.004736543310292274</v>
+        <v>0.0005272204427949623</v>
       </c>
       <c r="E42">
-        <v>0.9952634566897077</v>
+        <v>0.999472779557205</v>
       </c>
       <c r="F42">
-        <v>34.68117792562016</v>
+        <v>46.27766491481071</v>
       </c>
       <c r="G42">
-        <v>19499.30049947325</v>
+        <v>14045.58359775627</v>
       </c>
       <c r="H42">
-        <v>356224.5999371552</v>
+        <v>259249.9629554515</v>
       </c>
       <c r="I42">
-        <v>5249089.752980848</v>
+        <v>4047550.686337078</v>
       </c>
       <c r="J42">
-        <v>88.80700128476811</v>
+        <v>7.052494098783542</v>
       </c>
       <c r="K42">
-        <v>5798.354348044171</v>
+        <v>1700.347266544277</v>
       </c>
       <c r="L42">
-        <v>154336.5325148145</v>
+        <v>66509.45408225707</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2011,37 +2011,37 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>93173.12511343053</v>
+        <v>98828.61803061729</v>
       </c>
       <c r="C43">
-        <v>471.4835333505548</v>
+        <v>55.86902325921151</v>
       </c>
       <c r="D43">
-        <v>0.005060295367108947</v>
+        <v>0.0005653121977472475</v>
       </c>
       <c r="E43">
-        <v>0.9949397046328911</v>
+        <v>0.9994346878022528</v>
       </c>
       <c r="F43">
-        <v>33.84384905410708</v>
+        <v>45.30181256671293</v>
       </c>
       <c r="G43">
-        <v>18660.5204020549</v>
+        <v>13369.69378947862</v>
       </c>
       <c r="H43">
-        <v>336725.2994376819</v>
+        <v>245204.3793576952</v>
       </c>
       <c r="I43">
-        <v>4892865.153043693</v>
+        <v>3788300.723381627</v>
       </c>
       <c r="J43">
-        <v>90.79590859457727</v>
+        <v>7.198143789845601</v>
       </c>
       <c r="K43">
-        <v>5709.547346759403</v>
+        <v>1693.294772445494</v>
       </c>
       <c r="L43">
-        <v>148538.1781667703</v>
+        <v>64809.1068157128</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2049,37 +2049,37 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>92701.64158007997</v>
+        <v>98772.74900735808</v>
       </c>
       <c r="C44">
-        <v>501.2000871101878</v>
+        <v>60.06623699527086</v>
       </c>
       <c r="D44">
-        <v>0.00540659343855554</v>
+        <v>0.0006081255973831023</v>
       </c>
       <c r="E44">
-        <v>0.9945934065614445</v>
+        <v>0.9993918744026169</v>
       </c>
       <c r="F44">
-        <v>33.01343694380974</v>
+        <v>44.32715390360494</v>
       </c>
       <c r="G44">
-        <v>17852.01217030436</v>
+        <v>12725.8435604755</v>
       </c>
       <c r="H44">
-        <v>318064.779035627</v>
+        <v>231834.6855682167</v>
       </c>
       <c r="I44">
-        <v>4556139.853606012</v>
+        <v>3543096.344023932</v>
       </c>
       <c r="J44">
-        <v>92.80631910094344</v>
+        <v>7.370391635636258</v>
       </c>
       <c r="K44">
-        <v>5618.751438164827</v>
+        <v>1686.096628655648</v>
       </c>
       <c r="L44">
-        <v>142828.6308200108</v>
+        <v>63115.8120432673</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2087,37 +2087,37 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>92200.44149296978</v>
+        <v>98712.68277036281</v>
       </c>
       <c r="C45">
-        <v>532.6418484030771</v>
+        <v>64.7797705755454</v>
       </c>
       <c r="D45">
-        <v>0.005776998892610408</v>
+        <v>0.0006562456693254282</v>
       </c>
       <c r="E45">
-        <v>0.9942230011073896</v>
+        <v>0.9993437543306746</v>
       </c>
       <c r="F45">
-        <v>32.1901794535485</v>
+        <v>43.35382253563195</v>
       </c>
       <c r="G45">
-        <v>17072.5899984994</v>
+        <v>12112.48061834103</v>
       </c>
       <c r="H45">
-        <v>300212.7668653227</v>
+        <v>219108.8420077412</v>
       </c>
       <c r="I45">
-        <v>4238075.074570384</v>
+        <v>3311261.658455715</v>
       </c>
       <c r="J45">
-        <v>94.83493607242552</v>
+        <v>7.570250429118558</v>
       </c>
       <c r="K45">
-        <v>5525.945119063883</v>
+        <v>1678.726237020012</v>
       </c>
       <c r="L45">
-        <v>137209.879381846</v>
+        <v>61429.71541461165</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2125,37 +2125,37 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>91667.79964456671</v>
+        <v>98647.90299978726</v>
       </c>
       <c r="C46">
-        <v>565.8818238768519</v>
+        <v>70.07255156888313</v>
       </c>
       <c r="D46">
-        <v>0.006173179961458719</v>
+        <v>0.0007103298644780542</v>
       </c>
       <c r="E46">
-        <v>0.9938268200385413</v>
+        <v>0.9992896701355219</v>
       </c>
       <c r="F46">
-        <v>31.37431734957974</v>
+        <v>42.38196363856191</v>
       </c>
       <c r="G46">
-        <v>16321.11698556161</v>
+        <v>11528.12557656234</v>
       </c>
       <c r="H46">
-        <v>283140.1768668232</v>
+        <v>206996.3613894001</v>
       </c>
       <c r="I46">
-        <v>3937862.307705061</v>
+        <v>3092152.816447974</v>
       </c>
       <c r="J46">
-        <v>96.87806954220427</v>
+        <v>7.798830360462397</v>
       </c>
       <c r="K46">
-        <v>5431.110182991457</v>
+        <v>1671.155986590893</v>
       </c>
       <c r="L46">
-        <v>131683.9342627822</v>
+        <v>59750.98917759164</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2163,37 +2163,37 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>91101.91782068985</v>
+        <v>98577.83044821837</v>
       </c>
       <c r="C47">
-        <v>600.9919609467911</v>
+        <v>76.01504146213773</v>
       </c>
       <c r="D47">
-        <v>0.006596918872000979</v>
+        <v>0.0007711170058877226</v>
       </c>
       <c r="E47">
-        <v>0.993403081127999</v>
+        <v>0.9992288829941123</v>
       </c>
       <c r="F47">
-        <v>30.56609393815958</v>
+        <v>41.41173479545921</v>
       </c>
       <c r="G47">
-        <v>15596.50364734396</v>
+        <v>10971.36838541319</v>
       </c>
       <c r="H47">
-        <v>266819.0598812617</v>
+        <v>195468.2358128378</v>
       </c>
       <c r="I47">
-        <v>3654722.130838238</v>
+        <v>2885156.455058574</v>
       </c>
       <c r="J47">
-        <v>98.93160504653407</v>
+        <v>8.05734165700099</v>
       </c>
       <c r="K47">
-        <v>5334.232113449252</v>
+        <v>1663.357156230431</v>
       </c>
       <c r="L47">
-        <v>126252.8240797907</v>
+        <v>58079.83319100074</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2201,37 +2201,37 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>90500.92585974306</v>
+        <v>98501.81540675624</v>
       </c>
       <c r="C48">
-        <v>638.0423354123928</v>
+        <v>82.68610180573953</v>
       </c>
       <c r="D48">
-        <v>0.007050119425310863</v>
+        <v>0.0008394373389393195</v>
       </c>
       <c r="E48">
-        <v>0.9929498805746891</v>
+        <v>0.9991605626610607</v>
       </c>
       <c r="F48">
-        <v>29.765754666293</v>
+        <v>40.44330687566832</v>
       </c>
       <c r="G48">
-        <v>14897.70651739958</v>
+        <v>10440.86493016509</v>
       </c>
       <c r="H48">
-        <v>251222.5562339178</v>
+        <v>184496.8674274246</v>
       </c>
       <c r="I48">
-        <v>3387903.070956977</v>
+        <v>2689688.219245736</v>
       </c>
       <c r="J48">
-        <v>100.9909712604798</v>
+        <v>8.347097022097758</v>
       </c>
       <c r="K48">
-        <v>5235.300508402719</v>
+        <v>1655.29981457343</v>
       </c>
       <c r="L48">
-        <v>120918.5919663415</v>
+        <v>56416.47603477031</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2239,37 +2239,37 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>89862.88352433067</v>
+        <v>98419.1293049505</v>
       </c>
       <c r="C49">
-        <v>677.1002071538452</v>
+        <v>90.17395034379679</v>
       </c>
       <c r="D49">
-        <v>0.007534815049313637</v>
+        <v>0.000916223817266193</v>
       </c>
       <c r="E49">
-        <v>0.9924651849506864</v>
+        <v>0.9990837761827338</v>
       </c>
       <c r="F49">
-        <v>28.97354669034742</v>
+        <v>39.47686494880007</v>
       </c>
       <c r="G49">
-        <v>14223.72683393142</v>
+        <v>9935.333788849415</v>
       </c>
       <c r="H49">
-        <v>236324.8497165182</v>
+        <v>174056.0024972595</v>
       </c>
       <c r="I49">
-        <v>3136680.514723059</v>
+        <v>2505191.351818311</v>
       </c>
       <c r="J49">
-        <v>103.0511067361852</v>
+        <v>8.669513761746094</v>
       </c>
       <c r="K49">
-        <v>5134.309537142238</v>
+        <v>1646.952717551332</v>
       </c>
       <c r="L49">
-        <v>115683.2914579387</v>
+        <v>54761.17622019689</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2277,37 +2277,37 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>89185.78331717683</v>
+        <v>98328.9553546067</v>
       </c>
       <c r="C50">
-        <v>718.2289301203692</v>
+        <v>98.57721382670125</v>
       </c>
       <c r="D50">
-        <v>0.008053177349646501</v>
+        <v>0.001002524774835645</v>
       </c>
       <c r="E50">
-        <v>0.9919468226503535</v>
+        <v>0.9989974752251644</v>
       </c>
       <c r="F50">
-        <v>28.18971841240176</v>
+        <v>38.51260923055081</v>
       </c>
       <c r="G50">
-        <v>13573.60931050556</v>
+        <v>9453.553142285315</v>
       </c>
       <c r="H50">
-        <v>222101.1228825868</v>
+        <v>164120.6687084101</v>
       </c>
       <c r="I50">
-        <v>2900355.665006541</v>
+        <v>2331135.349321052</v>
       </c>
       <c r="J50">
-        <v>105.1064260118406</v>
+        <v>9.026115462253701</v>
       </c>
       <c r="K50">
-        <v>5031.258430406053</v>
+        <v>1638.283203789586</v>
       </c>
       <c r="L50">
-        <v>110548.9819207965</v>
+        <v>53114.22350264556</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2315,37 +2315,37 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>88467.55438705646</v>
+        <v>98230.37814078</v>
       </c>
       <c r="C51">
-        <v>761.4867023762833</v>
+        <v>108.006083903227</v>
       </c>
       <c r="D51">
-        <v>0.00860752518425778</v>
+        <v>0.001099518152606893</v>
       </c>
       <c r="E51">
-        <v>0.9913924748157422</v>
+        <v>0.9989004818473931</v>
       </c>
       <c r="F51">
-        <v>27.41451898441331</v>
+        <v>37.55075605619838</v>
       </c>
       <c r="G51">
-        <v>12946.44098793582</v>
+        <v>8994.357829571378</v>
       </c>
       <c r="H51">
-        <v>208527.5135720812</v>
+        <v>154667.1155661248</v>
       </c>
       <c r="I51">
-        <v>2678254.542123954</v>
+        <v>2167014.680612641</v>
       </c>
       <c r="J51">
-        <v>107.1507854328507</v>
+        <v>9.418533052053014</v>
       </c>
       <c r="K51">
-        <v>4926.152004394213</v>
+        <v>1629.257088327333</v>
       </c>
       <c r="L51">
-        <v>105517.7234903904</v>
+        <v>51475.94029885596</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2353,37 +2353,37 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>87706.06768468018</v>
+        <v>98122.37205687677</v>
       </c>
       <c r="C52">
-        <v>806.9251417656774</v>
+        <v>118.5835818678643</v>
       </c>
       <c r="D52">
-        <v>0.009200334287779555</v>
+        <v>0.001208527468120391</v>
       </c>
       <c r="E52">
-        <v>0.9907996657122204</v>
+        <v>0.9987914725318796</v>
       </c>
       <c r="F52">
-        <v>26.64819778051632</v>
+        <v>36.59153887650121</v>
       </c>
       <c r="G52">
-        <v>12341.35016450543</v>
+        <v>8556.636542730212</v>
       </c>
       <c r="H52">
-        <v>195581.0725841454</v>
+        <v>145672.7577365534</v>
       </c>
       <c r="I52">
-        <v>2469727.028551873</v>
+        <v>2012347.565046517</v>
       </c>
       <c r="J52">
-        <v>109.1774491115319</v>
+        <v>9.848505044392528</v>
       </c>
       <c r="K52">
-        <v>4819.001218961363</v>
+        <v>1619.83855527528</v>
       </c>
       <c r="L52">
-        <v>100591.5714859962</v>
+        <v>49846.68321052863</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2391,37 +2391,37 @@
         <v>51</v>
       </c>
       <c r="B53">
-        <v>86899.1425429145</v>
+        <v>98003.78847500891</v>
       </c>
       <c r="C53">
-        <v>854.5876728754076</v>
+        <v>130.4469369913162</v>
       </c>
       <c r="D53">
-        <v>0.009834247472043534</v>
+        <v>0.001331039738576845</v>
       </c>
       <c r="E53">
-        <v>0.9901657525279565</v>
+        <v>0.9986689602614232</v>
       </c>
       <c r="F53">
-        <v>25.89100383801614</v>
+        <v>35.63520926946964</v>
       </c>
       <c r="G53">
-        <v>11757.50540137446</v>
+        <v>8139.329154698667</v>
       </c>
       <c r="H53">
-        <v>183239.72241964</v>
+        <v>137116.1211938232</v>
       </c>
       <c r="I53">
-        <v>2274145.955967728</v>
+        <v>1866674.807309964</v>
       </c>
       <c r="J53">
-        <v>111.1790555490433</v>
+        <v>10.31787671453429</v>
       </c>
       <c r="K53">
-        <v>4709.823769849831</v>
+        <v>1609.990050230887</v>
       </c>
       <c r="L53">
-        <v>95772.57026703484</v>
+        <v>48226.84465525336</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2429,37 +2429,37 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>86044.55487003909</v>
+        <v>97873.3415380176</v>
       </c>
       <c r="C54">
-        <v>904.5077115157237</v>
+        <v>143.7490815514412</v>
       </c>
       <c r="D54">
-        <v>0.01051208542925097</v>
+        <v>0.001468725592613018</v>
       </c>
       <c r="E54">
-        <v>0.989487914570749</v>
+        <v>0.998531274407387</v>
       </c>
       <c r="F54">
-        <v>25.14318526791225</v>
+        <v>34.68203796007863</v>
       </c>
       <c r="G54">
-        <v>11194.11459961871</v>
+        <v>7741.424175379433</v>
       </c>
       <c r="H54">
-        <v>171482.2170182655</v>
+        <v>128976.7920391245</v>
       </c>
       <c r="I54">
-        <v>2090906.233548088</v>
+        <v>1729558.68611614</v>
       </c>
       <c r="J54">
-        <v>113.1475855538629</v>
+        <v>10.82859791395515</v>
       </c>
       <c r="K54">
-        <v>4598.644714300786</v>
+        <v>1599.672173516353</v>
       </c>
       <c r="L54">
-        <v>91062.74649718503</v>
+        <v>46616.85460502247</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2467,37 +2467,37 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>85140.04715852338</v>
+        <v>97729.59245646615</v>
       </c>
       <c r="C55">
-        <v>956.706634017176</v>
+        <v>158.6602633374356</v>
       </c>
       <c r="D55">
-        <v>0.01123685816424169</v>
+        <v>0.001623461833304085</v>
       </c>
       <c r="E55">
-        <v>0.9887631418357583</v>
+        <v>0.9983765381666959</v>
       </c>
       <c r="F55">
-        <v>24.40498863606915</v>
+        <v>33.73231583844497</v>
       </c>
       <c r="G55">
-        <v>10650.42414484874</v>
+        <v>7361.956331018837</v>
       </c>
       <c r="H55">
-        <v>160288.1024186468</v>
+        <v>121235.3678637451</v>
       </c>
       <c r="I55">
-        <v>1919424.016529822</v>
+        <v>1600581.894077016</v>
       </c>
       <c r="J55">
-        <v>115.0743322160388</v>
+        <v>11.38271916367662</v>
       </c>
       <c r="K55">
-        <v>4485.497128746923</v>
+        <v>1588.843575602398</v>
       </c>
       <c r="L55">
-        <v>86464.10178288425</v>
+        <v>45017.18243150611</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2505,37 +2505,37 @@
         <v>54</v>
       </c>
       <c r="B56">
-        <v>84183.3405245062</v>
+        <v>97570.93219312871</v>
       </c>
       <c r="C56">
-        <v>1011.191520394986</v>
+        <v>175.3697731078956</v>
       </c>
       <c r="D56">
-        <v>0.01201177708195866</v>
+        <v>0.001797356745150025</v>
       </c>
       <c r="E56">
-        <v>0.9879882229180413</v>
+        <v>0.99820264325485</v>
       </c>
       <c r="F56">
-        <v>23.67665831645649</v>
+        <v>32.78635496530094</v>
       </c>
       <c r="G56">
-        <v>10125.7181147539</v>
+        <v>7000.004262759025</v>
       </c>
       <c r="H56">
-        <v>149637.6782737981</v>
+        <v>113873.4115327262</v>
       </c>
       <c r="I56">
-        <v>1759135.914111175</v>
+        <v>1479346.526213271</v>
       </c>
       <c r="J56">
-        <v>116.9498738357448</v>
+        <v>11.98238559785606</v>
       </c>
       <c r="K56">
-        <v>4370.422796530886</v>
+        <v>1577.460856438721</v>
       </c>
       <c r="L56">
-        <v>81978.60465413732</v>
+        <v>43428.33885590371</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2543,37 +2543,37 @@
         <v>55</v>
       </c>
       <c r="B57">
-        <v>83172.14900411121</v>
+        <v>97395.56242002081</v>
       </c>
       <c r="C57">
-        <v>1067.952663016599</v>
+        <v>194.0877799782701</v>
       </c>
       <c r="D57">
-        <v>0.0128402677555417</v>
+        <v>0.00199277847117163</v>
       </c>
       <c r="E57">
-        <v>0.9871597322444583</v>
+        <v>0.9980072215288284</v>
       </c>
       <c r="F57">
-        <v>22.9584358181961</v>
+        <v>31.84448955176525</v>
       </c>
       <c r="G57">
-        <v>9619.317544196852</v>
+        <v>6654.68834083931</v>
       </c>
       <c r="H57">
-        <v>139511.9601590442</v>
+        <v>106873.4072699672</v>
       </c>
       <c r="I57">
-        <v>1609498.235837377</v>
+        <v>1365473.114680544</v>
       </c>
       <c r="J57">
-        <v>118.7640508587187</v>
+        <v>12.6298282456966</v>
       </c>
       <c r="K57">
-        <v>4253.47292269514</v>
+        <v>1565.478470840865</v>
       </c>
       <c r="L57">
-        <v>77608.18185760644</v>
+        <v>41850.877999465</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -2581,37 +2581,37 @@
         <v>56</v>
       </c>
       <c r="B58">
-        <v>82104.19634109462</v>
+        <v>97201.47464004254</v>
       </c>
       <c r="C58">
-        <v>1126.960836001979</v>
+        <v>215.0472616677226</v>
       </c>
       <c r="D58">
-        <v>0.01372598339943698</v>
+        <v>0.00221238682297864</v>
       </c>
       <c r="E58">
-        <v>0.986274016600563</v>
+        <v>0.9977876131770214</v>
       </c>
       <c r="F58">
-        <v>22.25055908848046</v>
+        <v>30.90707689845091</v>
       </c>
       <c r="G58">
-        <v>9130.579741638256</v>
+        <v>6325.168591601264</v>
       </c>
       <c r="H58">
-        <v>129892.6426148473</v>
+        <v>100218.7189291279</v>
       </c>
       <c r="I58">
-        <v>1469986.275678333</v>
+        <v>1258599.707410577</v>
       </c>
       <c r="J58">
-        <v>120.5059480393868</v>
+        <v>13.32735204302571</v>
       </c>
       <c r="K58">
-        <v>4134.708871836422</v>
+        <v>1552.848642595168</v>
       </c>
       <c r="L58">
-        <v>73354.70893491129</v>
+        <v>40285.39952862413</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -2619,37 +2619,37 @@
         <v>57</v>
       </c>
       <c r="B59">
-        <v>80977.23550509264</v>
+        <v>96986.42737837481</v>
       </c>
       <c r="C59">
-        <v>1188.164325387348</v>
+        <v>238.5060085499472</v>
       </c>
       <c r="D59">
-        <v>0.01467281907039941</v>
+        <v>0.002459168927003152</v>
       </c>
       <c r="E59">
-        <v>0.9853271809296006</v>
+        <v>0.9975408310729968</v>
       </c>
       <c r="F59">
-        <v>21.55326179376512</v>
+        <v>29.97449827687556</v>
       </c>
       <c r="G59">
-        <v>8658.897649689703</v>
+        <v>6010.642735196273</v>
       </c>
       <c r="H59">
-        <v>120762.062873209</v>
+        <v>93893.55033752663</v>
       </c>
       <c r="I59">
-        <v>1340093.633063486</v>
+        <v>1158380.988481449</v>
       </c>
       <c r="J59">
-        <v>122.1638832336574</v>
+        <v>14.07731985305896</v>
       </c>
       <c r="K59">
-        <v>4014.202923797036</v>
+        <v>1539.521290552143</v>
       </c>
       <c r="L59">
-        <v>69220.00006307487</v>
+        <v>38732.55088602896</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -2657,37 +2657,37 @@
         <v>58</v>
       </c>
       <c r="B60">
-        <v>79789.07117970529</v>
+        <v>96747.92136982486</v>
       </c>
       <c r="C60">
-        <v>1251.485726310962</v>
+        <v>264.7486700409052</v>
       </c>
       <c r="D60">
-        <v>0.01568492661723431</v>
+        <v>0.002736479154202054</v>
       </c>
       <c r="E60">
-        <v>0.9843150733827657</v>
+        <v>0.9972635208457979</v>
       </c>
       <c r="F60">
-        <v>20.86677258197887</v>
+        <v>29.04715973397454</v>
       </c>
       <c r="G60">
-        <v>8203.699241467979</v>
+        <v>5710.34433271482</v>
       </c>
       <c r="H60">
-        <v>112103.1652235193</v>
+        <v>87882.90760233036</v>
       </c>
       <c r="I60">
-        <v>1219331.570190276</v>
+        <v>1064487.438143923</v>
       </c>
       <c r="J60">
-        <v>123.7254044156596</v>
+        <v>14.88213164741899</v>
       </c>
       <c r="K60">
-        <v>3892.039040563379</v>
+        <v>1525.443970699084</v>
       </c>
       <c r="L60">
-        <v>65205.79713927782</v>
+        <v>37193.02959547682</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -2695,37 +2695,37 @@
         <v>59</v>
       </c>
       <c r="B61">
-        <v>78537.58545339433</v>
+        <v>96483.17269978396</v>
       </c>
       <c r="C61">
-        <v>1316.81852136393</v>
+        <v>294.0887984360795</v>
       </c>
       <c r="D61">
-        <v>0.01676673039745225</v>
+        <v>0.003048083828577686</v>
       </c>
       <c r="E61">
-        <v>0.9832332696025478</v>
+        <v>0.9969519161714223</v>
       </c>
       <c r="F61">
-        <v>20.19131432884086</v>
+        <v>28.12549279829583</v>
       </c>
       <c r="G61">
-        <v>7764.446943149705</v>
+        <v>5423.541042366695</v>
       </c>
       <c r="H61">
-        <v>103899.4659820514</v>
+        <v>82172.56326961555</v>
       </c>
       <c r="I61">
-        <v>1107228.404966757</v>
+        <v>976604.5305415925</v>
       </c>
       <c r="J61">
-        <v>125.1772967126089</v>
+        <v>15.74419785225265</v>
       </c>
       <c r="K61">
-        <v>3768.313636147719</v>
+        <v>1510.561839051665</v>
       </c>
       <c r="L61">
-        <v>61313.75809871444</v>
+        <v>35667.58562477773</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -2733,37 +2733,37 @@
         <v>60</v>
       </c>
       <c r="B62">
-        <v>77220.7669320304</v>
+        <v>96189.08390134788</v>
       </c>
       <c r="C62">
-        <v>1384.023464032941</v>
+        <v>326.8708281901125</v>
       </c>
       <c r="D62">
-        <v>0.01792294377561876</v>
+        <v>0.003398211261948947</v>
       </c>
       <c r="E62">
-        <v>0.9820770562243812</v>
+        <v>0.9966017887380511</v>
       </c>
       <c r="F62">
-        <v>19.52710337171634</v>
+        <v>27.2099550642177</v>
       </c>
       <c r="G62">
-        <v>7340.637071700568</v>
+        <v>5149.532985354123</v>
       </c>
       <c r="H62">
-        <v>96135.01903890166</v>
+        <v>76749.02222724885</v>
       </c>
       <c r="I62">
-        <v>1003328.938984706</v>
+        <v>894431.9672719771</v>
       </c>
       <c r="J62">
-        <v>126.5056014551077</v>
+        <v>16.66590569962663</v>
       </c>
       <c r="K62">
-        <v>3643.136339435111</v>
+        <v>1494.817641199412</v>
       </c>
       <c r="L62">
-        <v>57545.44446256671</v>
+        <v>34157.02378572607</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -2771,37 +2771,37 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>75836.74346799745</v>
+        <v>95862.21307315778</v>
       </c>
       <c r="C63">
-        <v>1452.924803082551</v>
+        <v>363.4719070015345</v>
       </c>
       <c r="D63">
-        <v>0.01915858641392842</v>
+        <v>0.003791607718508949</v>
       </c>
       <c r="E63">
-        <v>0.9808414135860716</v>
+        <v>0.9962083922814911</v>
       </c>
       <c r="F63">
-        <v>18.87434873477902</v>
+        <v>26.30103062833073</v>
       </c>
       <c r="G63">
-        <v>6931.799275180052</v>
+        <v>4887.651223209063</v>
       </c>
       <c r="H63">
-        <v>88794.3819672011</v>
+        <v>71599.48924189471</v>
       </c>
       <c r="I63">
-        <v>907193.9199458043</v>
+        <v>817682.9450447281</v>
       </c>
       <c r="J63">
-        <v>127.6956494399456</v>
+        <v>17.64957724123732</v>
       </c>
       <c r="K63">
-        <v>3516.630737980003</v>
+        <v>1478.151735499785</v>
       </c>
       <c r="L63">
-        <v>53902.3081231316</v>
+        <v>32662.20614452666</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -2809,37 +2809,37 @@
         <v>62</v>
       </c>
       <c r="B64">
-        <v>74383.8186649149</v>
+        <v>95498.74116615624</v>
       </c>
       <c r="C64">
-        <v>1523.306398007207</v>
+        <v>404.3034679956312</v>
       </c>
       <c r="D64">
-        <v>0.02047900236030387</v>
+        <v>0.004233599972717883</v>
       </c>
       <c r="E64">
-        <v>0.9795209976396961</v>
+        <v>0.9957664000272821</v>
       </c>
       <c r="F64">
-        <v>18.23325134957367</v>
+        <v>25.39923035002934</v>
       </c>
       <c r="G64">
-        <v>6537.495961310105</v>
+        <v>4637.256349624536</v>
       </c>
       <c r="H64">
-        <v>81862.58269202105</v>
+        <v>66711.83801868567</v>
       </c>
       <c r="I64">
-        <v>818399.5379786033</v>
+        <v>746083.4558028334</v>
       </c>
       <c r="J64">
-        <v>128.7321107905256</v>
+        <v>18.69741748119644</v>
       </c>
       <c r="K64">
-        <v>3388.935088540057</v>
+        <v>1460.502158258548</v>
       </c>
       <c r="L64">
-        <v>50385.6773851516</v>
+        <v>31184.05440902687</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -2847,37 +2847,37 @@
         <v>63</v>
       </c>
       <c r="B65">
-        <v>72860.5122669077</v>
+        <v>95094.4376981606</v>
       </c>
       <c r="C65">
-        <v>1594.907792515265</v>
+        <v>449.8123987439124</v>
       </c>
       <c r="D65">
-        <v>0.02188987893294914</v>
+        <v>0.004730165187701751</v>
       </c>
       <c r="E65">
-        <v>0.9781101210670509</v>
+        <v>0.9952698348122982</v>
       </c>
       <c r="F65">
-        <v>17.60400327538114</v>
+        <v>24.50509190644226</v>
       </c>
       <c r="G65">
-        <v>6157.321698161498</v>
+        <v>4397.737201208837</v>
       </c>
       <c r="H65">
-        <v>75325.08673071094</v>
+        <v>62074.58166906112</v>
       </c>
       <c r="I65">
-        <v>736536.9552865821</v>
+        <v>679371.6177841477</v>
       </c>
       <c r="J65">
-        <v>129.5990639653615</v>
+        <v>19.81145087030379</v>
       </c>
       <c r="K65">
-        <v>3260.202977749531</v>
+        <v>1441.804740777352</v>
       </c>
       <c r="L65">
-        <v>46996.74229661154</v>
+        <v>29723.55225076833</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -2885,37 +2885,37 @@
         <v>64</v>
       </c>
       <c r="B66">
-        <v>71265.60447439243</v>
+        <v>94644.62529941669</v>
       </c>
       <c r="C66">
-        <v>1667.420332517737</v>
+        <v>500.4816216792419</v>
       </c>
       <c r="D66">
-        <v>0.02339726639260997</v>
+        <v>0.00528800890801695</v>
       </c>
       <c r="E66">
-        <v>0.97660273360739</v>
+        <v>0.994711991091983</v>
       </c>
       <c r="F66">
-        <v>16.98678692407543</v>
+        <v>23.61917961019031</v>
       </c>
       <c r="G66">
-        <v>5790.902568882231</v>
+        <v>4168.509693138112</v>
       </c>
       <c r="H66">
-        <v>69167.76503254943</v>
+        <v>57676.84446785228</v>
       </c>
       <c r="I66">
-        <v>661211.8685558712</v>
+        <v>617297.0361150866</v>
       </c>
       <c r="J66">
-        <v>130.2800865940259</v>
+        <v>20.99344418139937</v>
       </c>
       <c r="K66">
-        <v>3130.603913784169</v>
+        <v>1421.993289907048</v>
       </c>
       <c r="L66">
-        <v>43736.53931886201</v>
+        <v>28281.74750999097</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -2923,37 +2923,37 @@
         <v>65</v>
       </c>
       <c r="B67">
-        <v>69598.18414187469</v>
+        <v>94144.14367773745</v>
       </c>
       <c r="C67">
-        <v>1740.48343731896</v>
+        <v>556.8298504742046</v>
       </c>
       <c r="D67">
-        <v>0.02500759838462185</v>
+        <v>0.005914652029554546</v>
       </c>
       <c r="E67">
-        <v>0.9749924016153781</v>
+        <v>0.9940853479704455</v>
       </c>
       <c r="F67">
-        <v>16.38177429442193</v>
+        <v>22.74208395719685</v>
       </c>
       <c r="G67">
-        <v>5437.895460408119</v>
+        <v>3949.015787378708</v>
       </c>
       <c r="H67">
-        <v>63376.8624636672</v>
+        <v>53508.33477471417</v>
       </c>
       <c r="I67">
-        <v>592044.1035233218</v>
+        <v>559620.1916472343</v>
       </c>
       <c r="J67">
-        <v>130.7583708956198</v>
+        <v>22.24481356339278</v>
       </c>
       <c r="K67">
-        <v>3000.323827190144</v>
+        <v>1400.999845725649</v>
       </c>
       <c r="L67">
-        <v>40605.93540507785</v>
+        <v>26859.75422008392</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -2961,37 +2961,37 @@
         <v>66</v>
       </c>
       <c r="B68">
-        <v>67857.70070455573</v>
+        <v>93587.31382726325</v>
       </c>
       <c r="C68">
-        <v>1813.68115754562</v>
+        <v>619.4102269918658</v>
       </c>
       <c r="D68">
-        <v>0.02672771312193689</v>
+        <v>0.006618527679244313</v>
       </c>
       <c r="E68">
-        <v>0.9732722868780631</v>
+        <v>0.9933814723207557</v>
       </c>
       <c r="F68">
-        <v>15.78912622099292</v>
+        <v>21.87442087101169</v>
       </c>
       <c r="G68">
-        <v>5097.987264112186</v>
+        <v>3738.722602987757</v>
       </c>
       <c r="H68">
-        <v>57938.96700325909</v>
+        <v>49559.31898733546</v>
       </c>
       <c r="I68">
-        <v>528667.2410596545</v>
+        <v>506111.8568725202</v>
       </c>
       <c r="J68">
-        <v>131.0168664369985</v>
+        <v>23.56651336465792</v>
       </c>
       <c r="K68">
-        <v>2869.565456294524</v>
+        <v>1378.755032162256</v>
       </c>
       <c r="L68">
-        <v>37605.61157788771</v>
+        <v>25458.75437435828</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -2999,37 +2999,37 @@
         <v>67</v>
       </c>
       <c r="B69">
-        <v>66044.0195470101</v>
+        <v>92967.90360027138</v>
       </c>
       <c r="C69">
-        <v>1886.539180523756</v>
+        <v>688.8074725005456</v>
       </c>
       <c r="D69">
-        <v>0.02856487526748608</v>
+        <v>0.00740908900626791</v>
       </c>
       <c r="E69">
-        <v>0.9714351247325139</v>
+        <v>0.9925909109937321</v>
       </c>
       <c r="F69">
-        <v>15.20899164306364</v>
+        <v>21.01683060997341</v>
       </c>
       <c r="G69">
-        <v>4770.893964440103</v>
+        <v>3537.121679957015</v>
       </c>
       <c r="H69">
-        <v>52840.9797391469</v>
+        <v>45820.59638434771</v>
       </c>
       <c r="I69">
-        <v>470728.2740563955</v>
+        <v>456552.5378851847</v>
       </c>
       <c r="J69">
-        <v>131.038452892917</v>
+        <v>24.95890414552515</v>
       </c>
       <c r="K69">
-        <v>2738.548589857525</v>
+        <v>1355.188518797598</v>
       </c>
       <c r="L69">
-        <v>34736.04612159319</v>
+        <v>24079.99934219602</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3037,37 +3037,37 @@
         <v>68</v>
       </c>
       <c r="B70">
-        <v>64157.48036648634</v>
+        <v>92279.09612777084</v>
       </c>
       <c r="C70">
-        <v>1958.522472796522</v>
+        <v>765.6331043484141</v>
       </c>
       <c r="D70">
-        <v>0.03052679845917994</v>
+        <v>0.008296928952233218</v>
       </c>
       <c r="E70">
-        <v>0.9694732015408201</v>
+        <v>0.9917030710477668</v>
       </c>
       <c r="F70">
-        <v>14.64150689899521</v>
+        <v>20.16997630416844</v>
       </c>
       <c r="G70">
-        <v>4456.359589837951</v>
+        <v>3343.728410099251</v>
       </c>
       <c r="H70">
-        <v>48070.08577470679</v>
+        <v>42283.47470439069</v>
       </c>
       <c r="I70">
-        <v>417887.2943172486</v>
+        <v>410731.941500837</v>
       </c>
       <c r="J70">
-        <v>130.8061452505931</v>
+        <v>26.42159719443545</v>
       </c>
       <c r="K70">
-        <v>2607.510136964609</v>
+        <v>1330.229614652073</v>
       </c>
       <c r="L70">
-        <v>31997.49753173566</v>
+        <v>22724.81082339842</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3075,37 +3075,37 @@
         <v>69</v>
       </c>
       <c r="B71">
-        <v>62198.95789368982</v>
+        <v>91513.46302342243</v>
       </c>
       <c r="C71">
-        <v>2029.033779438385</v>
+        <v>850.5181752728965</v>
       </c>
       <c r="D71">
-        <v>0.03262166840329384</v>
+        <v>0.009293913126806386</v>
       </c>
       <c r="E71">
-        <v>0.9673783315967062</v>
+        <v>0.9907060868731936</v>
       </c>
       <c r="F71">
-        <v>14.08679505170394</v>
+        <v>19.33454209069502</v>
       </c>
       <c r="G71">
-        <v>4154.154998824359</v>
+        <v>3158.081650519137</v>
       </c>
       <c r="H71">
-        <v>43613.72618486884</v>
+        <v>38939.74629429144</v>
       </c>
       <c r="I71">
-        <v>369817.2085425417</v>
+        <v>368448.4667964463</v>
       </c>
       <c r="J71">
-        <v>130.3033335264747</v>
+        <v>27.95327286408208</v>
       </c>
       <c r="K71">
-        <v>2476.703991714016</v>
+        <v>1303.808017457637</v>
       </c>
       <c r="L71">
-        <v>29389.98739477105</v>
+        <v>21394.58120874635</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3113,37 +3113,37 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>60169.92411425144</v>
+        <v>90662.94484814953</v>
       </c>
       <c r="C72">
-        <v>2097.413229552878</v>
+        <v>944.1028881455758</v>
       </c>
       <c r="D72">
-        <v>0.03485816644159767</v>
+        <v>0.01041332696314734</v>
       </c>
       <c r="E72">
-        <v>0.9651418335584023</v>
+        <v>0.9895866730368527</v>
       </c>
       <c r="F72">
-        <v>13.54496525085306</v>
+        <v>18.51123081835447</v>
       </c>
       <c r="G72">
-        <v>3864.076473035409</v>
+        <v>2979.743537154143</v>
       </c>
       <c r="H72">
-        <v>39459.57118604448</v>
+        <v>35781.6646437723</v>
       </c>
       <c r="I72">
-        <v>326203.4823576729</v>
+        <v>329508.7205021549</v>
       </c>
       <c r="J72">
-        <v>129.5140585001249</v>
+        <v>29.55147020829645</v>
       </c>
       <c r="K72">
-        <v>2346.400658187541</v>
+        <v>1275.854744593555</v>
       </c>
       <c r="L72">
-        <v>26913.28340305704</v>
+        <v>20090.77319128871</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3151,37 +3151,37 @@
         <v>71</v>
       </c>
       <c r="B73">
-        <v>58072.51088469856</v>
+        <v>89718.84196000396</v>
       </c>
       <c r="C73">
-        <v>2162.939325176322</v>
+        <v>1047.022327126771</v>
       </c>
       <c r="D73">
-        <v>0.03724549347402561</v>
+        <v>0.01167003835820268</v>
       </c>
       <c r="E73">
-        <v>0.9627545065259744</v>
+        <v>0.9883299616417973</v>
       </c>
       <c r="F73">
-        <v>13.01611213738119</v>
+        <v>17.70076129671536</v>
       </c>
       <c r="G73">
-        <v>3585.944088649306</v>
+        <v>2808.299517557555</v>
       </c>
       <c r="H73">
-        <v>35595.49471300907</v>
+        <v>32801.92110661816</v>
       </c>
       <c r="I73">
-        <v>286743.9111716285</v>
+        <v>293727.0558583826</v>
       </c>
       <c r="J73">
-        <v>128.4233241846235</v>
+        <v>31.21234580116072</v>
       </c>
       <c r="K73">
-        <v>2216.886599687416</v>
+        <v>1246.303274385259</v>
       </c>
       <c r="L73">
-        <v>24566.88274486949</v>
+        <v>18814.91844669516</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3189,37 +3189,37 @@
         <v>72</v>
       </c>
       <c r="B74">
-        <v>55909.57155952224</v>
+        <v>88671.81963287719</v>
       </c>
       <c r="C74">
-        <v>2224.831614558189</v>
+        <v>1159.887432394665</v>
       </c>
       <c r="D74">
-        <v>0.03979339409155724</v>
+        <v>0.01308067700873716</v>
       </c>
       <c r="E74">
-        <v>0.9602066059084428</v>
+        <v>0.9869193229912628</v>
       </c>
       <c r="F74">
-        <v>12.50031529589471</v>
+        <v>16.90386506965927</v>
       </c>
       <c r="G74">
-        <v>3319.59983797817</v>
+        <v>2643.358623301272</v>
       </c>
       <c r="H74">
-        <v>32009.55062435977</v>
+        <v>29993.6215890606</v>
       </c>
       <c r="I74">
-        <v>251148.4164586194</v>
+        <v>260925.1347517644</v>
       </c>
       <c r="J74">
-        <v>127.0174467105143</v>
+        <v>32.93040035206101</v>
       </c>
       <c r="K74">
-        <v>2088.463275502792</v>
+        <v>1215.090928584098</v>
       </c>
       <c r="L74">
-        <v>22349.99614518208</v>
+        <v>17568.6151723099</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3227,37 +3227,37 @@
         <v>73</v>
       </c>
       <c r="B75">
-        <v>53684.73994496404</v>
+        <v>87511.93220048252</v>
       </c>
       <c r="C75">
-        <v>2282.255367674975</v>
+        <v>1283.260238960788</v>
       </c>
       <c r="D75">
-        <v>0.04251218074288288</v>
+        <v>0.01466383162493712</v>
       </c>
       <c r="E75">
-        <v>0.9574878192571171</v>
+        <v>0.9853361683750629</v>
       </c>
       <c r="F75">
-        <v>11.99763876029714</v>
+        <v>16.12128270013059</v>
       </c>
       <c r="G75">
-        <v>3064.905474422341</v>
+        <v>2484.554002792007</v>
       </c>
       <c r="H75">
-        <v>28689.9507863816</v>
+        <v>27350.26296575933</v>
       </c>
       <c r="I75">
-        <v>219138.8658342596</v>
+        <v>230931.5131627038</v>
       </c>
       <c r="J75">
-        <v>125.2844379697055</v>
+        <v>34.69817291429099</v>
       </c>
       <c r="K75">
-        <v>1961.445828792278</v>
+        <v>1182.160528232037</v>
       </c>
       <c r="L75">
-        <v>20261.53286967929</v>
+        <v>16353.5242437258</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3265,37 +3265,37 @@
         <v>74</v>
       </c>
       <c r="B76">
-        <v>51402.48457728907</v>
+        <v>86228.67196152173</v>
       </c>
       <c r="C76">
-        <v>2334.328578464405</v>
+        <v>1417.622314800884</v>
       </c>
       <c r="D76">
-        <v>0.04541275772291697</v>
+        <v>0.01644026612671801</v>
       </c>
       <c r="E76">
-        <v>0.954587242277083</v>
+        <v>0.983559733873282</v>
       </c>
       <c r="F76">
-        <v>11.50813057780491</v>
+        <v>15.35375956095467</v>
       </c>
       <c r="G76">
-        <v>2821.740056667161</v>
+        <v>2331.543734506668</v>
       </c>
       <c r="H76">
-        <v>25625.04531195926</v>
+        <v>24865.70896296732</v>
       </c>
       <c r="I76">
-        <v>190448.915047878</v>
+        <v>203581.2501969445</v>
       </c>
       <c r="J76">
-        <v>123.2144207216113</v>
+        <v>36.50590426797293</v>
       </c>
       <c r="K76">
-        <v>1836.161390822572</v>
+        <v>1147.462355317746</v>
       </c>
       <c r="L76">
-        <v>18300.08704088701</v>
+        <v>15171.36371549376</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3303,37 +3303,37 @@
         <v>75</v>
       </c>
       <c r="B77">
-        <v>49068.15599882467</v>
+        <v>84811.04964672084</v>
       </c>
       <c r="C77">
-        <v>2380.131610631949</v>
+        <v>1563.335290620649</v>
       </c>
       <c r="D77">
-        <v>0.04850664473083033</v>
+        <v>0.01843315578727889</v>
       </c>
       <c r="E77">
-        <v>0.9514933552691697</v>
+        <v>0.9815668442127211</v>
       </c>
       <c r="F77">
-        <v>11.03182243620395</v>
+        <v>14.60204113629195</v>
       </c>
       <c r="G77">
-        <v>2589.997172227582</v>
+        <v>2184.01193811933</v>
       </c>
       <c r="H77">
-        <v>22803.3052552921</v>
+        <v>22534.16522846066</v>
       </c>
       <c r="I77">
-        <v>164823.8697359188</v>
+        <v>178715.5412339772</v>
       </c>
       <c r="J77">
-        <v>120.8000698914408</v>
+        <v>38.34117361583858</v>
       </c>
       <c r="K77">
-        <v>1712.946970100961</v>
+        <v>1110.956451049773</v>
       </c>
       <c r="L77">
-        <v>16463.92565006444</v>
+        <v>14023.90136017602</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3341,37 +3341,37 @@
         <v>76</v>
       </c>
       <c r="B78">
-        <v>46688.02438819272</v>
+        <v>83247.71435610019</v>
       </c>
       <c r="C78">
-        <v>2418.719777425104</v>
+        <v>1720.59240281539</v>
       </c>
       <c r="D78">
-        <v>0.05180599969950306</v>
+        <v>0.02066834406354257</v>
       </c>
       <c r="E78">
-        <v>0.9481940003004969</v>
+        <v>0.9793316559364574</v>
       </c>
       <c r="F78">
-        <v>10.56872935883465</v>
+        <v>13.86686784953773</v>
       </c>
       <c r="G78">
-        <v>2369.581826481234</v>
+        <v>2041.670196021618</v>
       </c>
       <c r="H78">
-        <v>20213.30808306452</v>
+        <v>20350.15329034133</v>
       </c>
       <c r="I78">
-        <v>142020.5644806267</v>
+        <v>156181.3760055165</v>
       </c>
       <c r="J78">
-        <v>118.0370724909949</v>
+        <v>40.18851626252876</v>
       </c>
       <c r="K78">
-        <v>1592.14690020952</v>
+        <v>1072.615277433934</v>
       </c>
       <c r="L78">
-        <v>14750.97867996348</v>
+        <v>12912.94490912624</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3379,37 +3379,37 @@
         <v>77</v>
       </c>
       <c r="B79">
-        <v>44269.30461076761</v>
+        <v>81527.12195328479</v>
       </c>
       <c r="C79">
-        <v>2449.13909553661</v>
+        <v>1889.360113222323</v>
       </c>
       <c r="D79">
-        <v>0.05532364054665784</v>
+        <v>0.02317462051837094</v>
       </c>
       <c r="E79">
-        <v>0.9446763594533422</v>
+        <v>0.9768253794816291</v>
       </c>
       <c r="F79">
-        <v>10.11884947135683</v>
+        <v>13.14896944616382</v>
       </c>
       <c r="G79">
-        <v>2160.406991433268</v>
+        <v>1904.259289472345</v>
       </c>
       <c r="H79">
-        <v>17843.72625658329</v>
+        <v>18308.48309431971</v>
       </c>
       <c r="I79">
-        <v>121807.2563975622</v>
+        <v>135831.2227151752</v>
       </c>
       <c r="J79">
-        <v>114.9245959889814</v>
+        <v>42.02903466867073</v>
       </c>
       <c r="K79">
-        <v>1474.109827718525</v>
+        <v>1032.426761171406</v>
       </c>
       <c r="L79">
-        <v>13158.83177975396</v>
+        <v>11840.32963169231</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3417,37 +3417,37 @@
         <v>78</v>
       </c>
       <c r="B80">
-        <v>41820.165515231</v>
+        <v>79637.76184006246</v>
       </c>
       <c r="C80">
-        <v>2470.445374187933</v>
+        <v>2069.309177549417</v>
       </c>
       <c r="D80">
-        <v>0.05907306543988189</v>
+        <v>0.02598401976320275</v>
       </c>
       <c r="E80">
-        <v>0.9409269345601181</v>
+        <v>0.9740159802367973</v>
       </c>
       <c r="F80">
-        <v>9.68216384384065</v>
+        <v>12.44905897395524</v>
       </c>
       <c r="G80">
-        <v>1962.389818850699</v>
+        <v>1771.551241019277</v>
       </c>
       <c r="H80">
-        <v>15683.31926515001</v>
+        <v>16404.22380484736</v>
       </c>
       <c r="I80">
-        <v>103963.5301409789</v>
+        <v>117522.7396208555</v>
       </c>
       <c r="J80">
-        <v>111.4657521033897</v>
+        <v>43.84002138873453</v>
       </c>
       <c r="K80">
-        <v>1359.185231729543</v>
+        <v>990.3977265027349</v>
       </c>
       <c r="L80">
-        <v>11684.72195203543</v>
+        <v>10807.9028705209</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3455,37 +3455,37 @@
         <v>79</v>
       </c>
       <c r="B81">
-        <v>39349.72014104307</v>
+        <v>77568.45266251305</v>
       </c>
       <c r="C81">
-        <v>2481.726687618262</v>
+        <v>2259.735076312524</v>
       </c>
       <c r="D81">
-        <v>0.06306847110279035</v>
+        <v>0.02913214069312742</v>
       </c>
       <c r="E81">
-        <v>0.9369315288972097</v>
+        <v>0.9708678593068726</v>
       </c>
       <c r="F81">
-        <v>9.258636411161191</v>
+        <v>11.76782641805348</v>
       </c>
       <c r="G81">
-        <v>1775.447535253052</v>
+        <v>1643.351636724863</v>
       </c>
       <c r="H81">
-        <v>13720.92944629931</v>
+        <v>14632.67256382809</v>
       </c>
       <c r="I81">
-        <v>88280.21087582884</v>
+        <v>101118.5158160081</v>
       </c>
       <c r="J81">
-        <v>107.6680399727187</v>
+        <v>45.59462008509516</v>
       </c>
       <c r="K81">
-        <v>1247.719479626154</v>
+        <v>946.5577051140004</v>
       </c>
       <c r="L81">
-        <v>10325.53672030589</v>
+        <v>9817.505144018169</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3493,37 +3493,37 @@
         <v>80</v>
       </c>
       <c r="B82">
-        <v>36867.99345342481</v>
+        <v>75308.71758620052</v>
       </c>
       <c r="C82">
-        <v>2482.129128633119</v>
+        <v>2459.468578625294</v>
       </c>
       <c r="D82">
-        <v>0.06732476861722303</v>
+        <v>0.03265848440202312</v>
       </c>
       <c r="E82">
-        <v>0.932675231382777</v>
+        <v>0.9673415155979769</v>
       </c>
       <c r="F82">
-        <v>8.848213974046013</v>
+        <v>11.10593206381131</v>
       </c>
       <c r="G82">
-        <v>1599.493051616754</v>
+        <v>1519.502176795726</v>
       </c>
       <c r="H82">
-        <v>11945.48191104626</v>
+        <v>12989.32092710322</v>
       </c>
       <c r="I82">
-        <v>74559.28142952954</v>
+        <v>86485.84325218006</v>
       </c>
       <c r="J82">
-        <v>103.543749620148</v>
+        <v>47.26156013306991</v>
       </c>
       <c r="K82">
-        <v>1140.051439653435</v>
+        <v>900.9630850289052</v>
       </c>
       <c r="L82">
-        <v>9077.817240679735</v>
+        <v>8870.947438904168</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3531,37 +3531,37 @@
         <v>81</v>
       </c>
       <c r="B83">
-        <v>34385.86432479169</v>
+        <v>72849.24900757523</v>
       </c>
       <c r="C83">
-        <v>2470.885550067378</v>
+        <v>2666.778471084772</v>
       </c>
       <c r="D83">
-        <v>0.07185759609613496</v>
+        <v>0.03660680799616023</v>
       </c>
       <c r="E83">
-        <v>0.928142403903865</v>
+        <v>0.9633931920038398</v>
       </c>
       <c r="F83">
-        <v>8.450826282444552</v>
+        <v>10.46399967622096</v>
       </c>
       <c r="G83">
-        <v>1434.430338472885</v>
+        <v>1399.883370148574</v>
       </c>
       <c r="H83">
-        <v>10345.98885942951</v>
+        <v>11469.8187503075</v>
       </c>
       <c r="I83">
-        <v>62613.79951848328</v>
+        <v>73496.52232507683</v>
       </c>
       <c r="J83">
-        <v>99.11030374041027</v>
+        <v>48.80501118861577</v>
       </c>
       <c r="K83">
-        <v>1036.507690033287</v>
+        <v>853.7015248958353</v>
       </c>
       <c r="L83">
-        <v>7937.765801026301</v>
+        <v>7969.984353875263</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3569,37 +3569,37 @@
         <v>82</v>
       </c>
       <c r="B84">
-        <v>31914.97877472431</v>
+        <v>70182.47053649045</v>
       </c>
       <c r="C84">
-        <v>2447.346769964409</v>
+        <v>2879.270243354999</v>
       </c>
       <c r="D84">
-        <v>0.07668332751336915</v>
+        <v>0.04102549000263478</v>
       </c>
       <c r="E84">
-        <v>0.9233166724866309</v>
+        <v>0.9589745099973652</v>
       </c>
       <c r="F84">
-        <v>8.066386202163097</v>
+        <v>9.842609600028446</v>
       </c>
       <c r="G84">
-        <v>1280.149637098902</v>
+        <v>1284.41724609574</v>
       </c>
       <c r="H84">
-        <v>8911.558520956625</v>
+        <v>10069.93538015892</v>
       </c>
       <c r="I84">
-        <v>52267.81065905377</v>
+        <v>62026.70357476932</v>
       </c>
       <c r="J84">
-        <v>94.39051335363051</v>
+        <v>50.18461608467856</v>
       </c>
       <c r="K84">
-        <v>937.3973862928767</v>
+        <v>804.8965137072196</v>
       </c>
       <c r="L84">
-        <v>6901.258110993013</v>
+        <v>7116.282828979428</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3607,37 +3607,37 @@
         <v>83</v>
       </c>
       <c r="B85">
-        <v>29467.6320047599</v>
+        <v>67303.20029313545</v>
       </c>
       <c r="C85">
-        <v>2411.014448453616</v>
+        <v>3093.786855754113</v>
       </c>
       <c r="D85">
-        <v>0.08181907687947798</v>
+        <v>0.04596790111434956</v>
       </c>
       <c r="E85">
-        <v>0.918180923120522</v>
+        <v>0.9540320988856504</v>
       </c>
       <c r="F85">
-        <v>7.694789964948515</v>
+        <v>9.24229189893078</v>
       </c>
       <c r="G85">
-        <v>1136.522599241467</v>
+        <v>1173.069904006503</v>
       </c>
       <c r="H85">
-        <v>7631.408883857723</v>
+        <v>8785.518134063183</v>
       </c>
       <c r="I85">
-        <v>43356.25213809714</v>
+        <v>51956.7681946104</v>
       </c>
       <c r="J85">
-        <v>89.41272107942473</v>
+        <v>51.3557727119909</v>
       </c>
       <c r="K85">
-        <v>843.0068729392463</v>
+        <v>754.7118976225411</v>
       </c>
       <c r="L85">
-        <v>5963.860724700137</v>
+        <v>6311.386315272208</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -3645,37 +3645,37 @@
         <v>84</v>
       </c>
       <c r="B86">
-        <v>27056.61755630629</v>
+        <v>64209.41343738134</v>
       </c>
       <c r="C86">
-        <v>2361.574547873419</v>
+        <v>3306.320656460233</v>
       </c>
       <c r="D86">
-        <v>0.08728269684704137</v>
+        <v>0.05149277153395337</v>
       </c>
       <c r="E86">
-        <v>0.9127173031529586</v>
+        <v>0.9485072284660466</v>
       </c>
       <c r="F86">
-        <v>7.335917501418305</v>
+        <v>8.663519664738896</v>
       </c>
       <c r="G86">
-        <v>1003.397470498909</v>
+        <v>1065.853659675154</v>
       </c>
       <c r="H86">
-        <v>6494.886284616255</v>
+        <v>7612.44823005668</v>
       </c>
       <c r="I86">
-        <v>35724.84325423942</v>
+        <v>43171.25006054722</v>
       </c>
       <c r="J86">
-        <v>84.21080503331191</v>
+        <v>52.27024665360077</v>
       </c>
       <c r="K86">
-        <v>753.5941518598214</v>
+        <v>703.3561249105501</v>
       </c>
       <c r="L86">
-        <v>5120.853851760892</v>
+        <v>5556.674417649667</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -3683,37 +3683,37 @@
         <v>85</v>
       </c>
       <c r="B87">
-        <v>24695.04300843287</v>
+        <v>60903.09278092111</v>
       </c>
       <c r="C87">
-        <v>2298.929976570143</v>
+        <v>3511.949016842887</v>
       </c>
       <c r="D87">
-        <v>0.09309277071455613</v>
+        <v>0.05766454307133417</v>
       </c>
       <c r="E87">
-        <v>0.9069072292854439</v>
+        <v>0.9423354569286658</v>
       </c>
       <c r="F87">
-        <v>6.989632855434868</v>
+        <v>8.10670263730217</v>
       </c>
       <c r="G87">
-        <v>880.5944550617927</v>
+        <v>962.8284768465462</v>
       </c>
       <c r="H87">
-        <v>5491.488814117346</v>
+        <v>6546.594570381525</v>
       </c>
       <c r="I87">
-        <v>29229.95696962317</v>
+        <v>35558.80183049054</v>
       </c>
       <c r="J87">
-        <v>78.82401701690091</v>
+        <v>52.87720397469023</v>
       </c>
       <c r="K87">
-        <v>669.3833468265096</v>
+        <v>651.0858782569494</v>
       </c>
       <c r="L87">
-        <v>4367.259699901071</v>
+        <v>4853.318292739117</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -3721,37 +3721,37 @@
         <v>86</v>
       </c>
       <c r="B88">
-        <v>22396.11303186272</v>
+        <v>57391.14376407822</v>
       </c>
       <c r="C88">
-        <v>2223.230711652836</v>
+        <v>3704.810120460977</v>
       </c>
       <c r="D88">
-        <v>0.09926859667522969</v>
+        <v>0.0645536902991618</v>
       </c>
       <c r="E88">
-        <v>0.9007314033247703</v>
+        <v>0.9354463097008382</v>
       </c>
       <c r="F88">
-        <v>6.655784677720651</v>
+        <v>7.572181282549356</v>
       </c>
       <c r="G88">
-        <v>767.901420542515</v>
+        <v>864.1022977839252</v>
       </c>
       <c r="H88">
-        <v>4610.894359055554</v>
+        <v>5583.76609353498</v>
       </c>
       <c r="I88">
-        <v>23738.46815550582</v>
+        <v>29012.20726010901</v>
       </c>
       <c r="J88">
-        <v>73.29663115593351</v>
+        <v>53.1247543980358</v>
       </c>
       <c r="K88">
-        <v>590.5593298096087</v>
+        <v>598.208674282259</v>
       </c>
       <c r="L88">
-        <v>3697.87635307456</v>
+        <v>4202.232414482168</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -3759,37 +3759,37 @@
         <v>87</v>
       </c>
       <c r="B89">
-        <v>20172.88232020989</v>
+        <v>53686.33364361724</v>
       </c>
       <c r="C89">
-        <v>2134.899424662352</v>
+        <v>3878.139165823952</v>
       </c>
       <c r="D89">
-        <v>0.1058301630265069</v>
+        <v>0.07223699035899844</v>
       </c>
       <c r="E89">
-        <v>0.8941698369734931</v>
+        <v>0.9277630096410016</v>
       </c>
       <c r="F89">
-        <v>6.3342067957201</v>
+        <v>7.060221478463134</v>
       </c>
       <c r="G89">
-        <v>665.0701193657154</v>
+        <v>769.8298149199882</v>
       </c>
       <c r="H89">
-        <v>3842.99293851304</v>
+        <v>4719.663795751055</v>
       </c>
       <c r="I89">
-        <v>19127.57379645027</v>
+        <v>23428.44116657403</v>
       </c>
       <c r="J89">
-        <v>67.67738380435779</v>
+        <v>52.96208468423308</v>
       </c>
       <c r="K89">
-        <v>517.2626986536753</v>
+        <v>545.0839198842233</v>
       </c>
       <c r="L89">
-        <v>3107.317023264951</v>
+        <v>3604.023740199909</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -3797,37 +3797,37 @@
         <v>88</v>
       </c>
       <c r="B90">
-        <v>18037.98289554754</v>
+        <v>49808.19447779329</v>
       </c>
       <c r="C90">
-        <v>2034.650431481878</v>
+        <v>4024.388317951662</v>
       </c>
       <c r="D90">
-        <v>0.1127981129189399</v>
+        <v>0.08079771531862923</v>
       </c>
       <c r="E90">
-        <v>0.8872018870810601</v>
+        <v>0.9192022846813708</v>
       </c>
       <c r="F90">
-        <v>6.024718855947106</v>
+        <v>6.571009956520703</v>
       </c>
       <c r="G90">
-        <v>571.8131155857533</v>
+        <v>680.2091676205175</v>
       </c>
       <c r="H90">
-        <v>3177.922819147324</v>
+        <v>3949.833980831067</v>
       </c>
       <c r="I90">
-        <v>15284.58085793723</v>
+        <v>18708.77737082298</v>
       </c>
       <c r="J90">
-        <v>62.01869267343523</v>
+        <v>52.34223493573745</v>
       </c>
       <c r="K90">
-        <v>449.5853148493175</v>
+        <v>492.1218351999902</v>
       </c>
       <c r="L90">
-        <v>2590.054324611276</v>
+        <v>3058.939820315685</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -3835,37 +3835,37 @@
         <v>89</v>
       </c>
       <c r="B91">
-        <v>16003.33246406566</v>
+        <v>45783.80615984162</v>
       </c>
       <c r="C91">
-        <v>1923.49969446613</v>
+        <v>4135.454990417877</v>
       </c>
       <c r="D91">
-        <v>0.1201936970806057</v>
+        <v>0.09032571420515079</v>
       </c>
       <c r="E91">
-        <v>0.8798063029193943</v>
+        <v>0.9096742857948492</v>
       </c>
       <c r="F91">
-        <v>5.727127034325541</v>
+        <v>6.104650638597072</v>
       </c>
       <c r="G91">
-        <v>487.8016107744044</v>
+        <v>595.4760199409459</v>
       </c>
       <c r="H91">
-        <v>2606.109703561571</v>
+        <v>3269.624813210549</v>
       </c>
       <c r="I91">
-        <v>12106.6580387899</v>
+        <v>14758.94338999191</v>
       </c>
       <c r="J91">
-        <v>56.37565292389449</v>
+        <v>51.2255207554348</v>
       </c>
       <c r="K91">
-        <v>387.5666221758823</v>
+        <v>439.7796002642527</v>
       </c>
       <c r="L91">
-        <v>2140.469009761958</v>
+        <v>2566.817985115695</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -3873,37 +3873,37 @@
         <v>90</v>
       </c>
       <c r="B92">
-        <v>14079.83276959953</v>
+        <v>41648.35116942375</v>
       </c>
       <c r="C92">
-        <v>1802.763664369774</v>
+        <v>4203.040978083322</v>
       </c>
       <c r="D92">
-        <v>0.128038712807883</v>
+        <v>0.1009173439060175</v>
       </c>
       <c r="E92">
-        <v>0.871961287192117</v>
+        <v>0.8990826560939825</v>
       </c>
       <c r="F92">
-        <v>5.441224809348106</v>
+        <v>5.66116199624119</v>
       </c>
       <c r="G92">
-        <v>412.6643574361096</v>
+        <v>515.8944982359421</v>
       </c>
       <c r="H92">
-        <v>2118.308092787167</v>
+        <v>2674.148793269603</v>
       </c>
       <c r="I92">
-        <v>9500.54833522833</v>
+        <v>11489.31857678136</v>
       </c>
       <c r="J92">
-        <v>50.80482033443427</v>
+        <v>49.58352618828467</v>
       </c>
       <c r="K92">
-        <v>331.1909692519877</v>
+        <v>388.5540795088179</v>
       </c>
       <c r="L92">
-        <v>1752.902387586076</v>
+        <v>2127.038384851443</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -3911,37 +3911,37 @@
         <v>91</v>
       </c>
       <c r="B93">
-        <v>12277.06910522975</v>
+        <v>37445.31019134042</v>
       </c>
       <c r="C93">
-        <v>1674.045004669849</v>
+        <v>4219.157778535268</v>
       </c>
       <c r="D93">
-        <v>0.1363554273679818</v>
+        <v>0.1126751990296234</v>
       </c>
       <c r="E93">
-        <v>0.8636445726320182</v>
+        <v>0.8873248009703766</v>
       </c>
       <c r="F93">
-        <v>5.166793792256307</v>
+        <v>5.240475540551064</v>
       </c>
       <c r="G93">
-        <v>345.9878310464404</v>
+        <v>441.7445673697554</v>
       </c>
       <c r="H93">
-        <v>1705.643735351057</v>
+        <v>2158.254295033661</v>
       </c>
       <c r="I93">
-        <v>7382.240242441165</v>
+        <v>8815.169783511756</v>
       </c>
       <c r="J93">
-        <v>45.36280631390236</v>
+        <v>47.40348290346864</v>
       </c>
       <c r="K93">
-        <v>280.3861489175535</v>
+        <v>338.9705533205333</v>
       </c>
       <c r="L93">
-        <v>1421.711418334088</v>
+        <v>1738.484305342625</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -3949,37 +3949,37 @@
         <v>92</v>
       </c>
       <c r="B94">
-        <v>10603.02410055991</v>
+        <v>33226.15241280515</v>
       </c>
       <c r="C94">
-        <v>1539.203726505986</v>
+        <v>4176.779233632662</v>
       </c>
       <c r="D94">
-        <v>0.145166483817075</v>
+        <v>0.1257075806352757</v>
       </c>
       <c r="E94">
-        <v>0.854833516182925</v>
+        <v>0.8742924193647243</v>
       </c>
       <c r="F94">
-        <v>4.903604607893176</v>
+        <v>4.842435526840782</v>
       </c>
       <c r="G94">
-        <v>287.3178004615211</v>
+        <v>373.3056288772507</v>
       </c>
       <c r="H94">
-        <v>1359.655904304616</v>
+        <v>1716.509727663906</v>
       </c>
       <c r="I94">
-        <v>5676.596507090108</v>
+        <v>6656.915488478096</v>
       </c>
       <c r="J94">
-        <v>40.10472579909133</v>
+        <v>44.69271185113265</v>
       </c>
       <c r="K94">
-        <v>235.0233426036511</v>
+        <v>291.5670704170647</v>
       </c>
       <c r="L94">
-        <v>1141.325269416534</v>
+        <v>1399.513752022091</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -3987,37 +3987,37 @@
         <v>93</v>
       </c>
       <c r="B95">
-        <v>9063.820374053919</v>
+        <v>29049.37317917249</v>
       </c>
       <c r="C95">
-        <v>1400.312999049603</v>
+        <v>4070.619895601847</v>
       </c>
       <c r="D95">
-        <v>0.1544947871052407</v>
+        <v>0.1401276327201565</v>
       </c>
       <c r="E95">
-        <v>0.8455052128947593</v>
+        <v>0.8598723672798435</v>
       </c>
       <c r="F95">
-        <v>4.651417819409474</v>
+        <v>4.466799929474476</v>
       </c>
       <c r="G95">
-        <v>236.1623900292943</v>
+        <v>310.8364585081537</v>
       </c>
       <c r="H95">
-        <v>1072.338103843095</v>
+        <v>1343.204098786655</v>
       </c>
       <c r="I95">
-        <v>4316.940602785493</v>
+        <v>4940.405760814191</v>
       </c>
       <c r="J95">
-        <v>35.08255593253907</v>
+        <v>41.48264485129974</v>
       </c>
       <c r="K95">
-        <v>194.9186168045598</v>
+        <v>246.874358565932</v>
       </c>
       <c r="L95">
-        <v>906.3019268128836</v>
+        <v>1107.946681605027</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4025,37 +4025,37 @@
         <v>94</v>
       </c>
       <c r="B96">
-        <v>7663.507375004317</v>
+        <v>24978.75328357064</v>
       </c>
       <c r="C96">
-        <v>1259.599884549784</v>
+        <v>3897.986004901254</v>
       </c>
       <c r="D96">
-        <v>0.1643633682219917</v>
+        <v>0.1560520639540921</v>
       </c>
       <c r="E96">
-        <v>0.8356366317780083</v>
+        <v>0.8439479360459079</v>
       </c>
       <c r="F96">
-        <v>4.409984889621496</v>
+        <v>4.113242709523528</v>
       </c>
       <c r="G96">
-        <v>191.9966652494747</v>
+        <v>254.5520775374181</v>
       </c>
       <c r="H96">
-        <v>836.1757138138008</v>
+        <v>1032.367640278501</v>
       </c>
       <c r="I96">
-        <v>3244.602498942397</v>
+        <v>3597.201662027536</v>
       </c>
       <c r="J96">
-        <v>30.34347941134027</v>
+        <v>37.83178769858684</v>
       </c>
       <c r="K96">
-        <v>159.8360608720207</v>
+        <v>205.3917137146323</v>
       </c>
       <c r="L96">
-        <v>711.3833100083239</v>
+        <v>861.0723230390945</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4063,37 +4063,37 @@
         <v>95</v>
       </c>
       <c r="B97">
-        <v>6403.907490454533</v>
+        <v>21080.76727866939</v>
       </c>
       <c r="C97">
-        <v>1119.372444536985</v>
+        <v>3659.607732467544</v>
       </c>
       <c r="D97">
-        <v>0.1747952240418037</v>
+        <v>0.1735993611660674</v>
       </c>
       <c r="E97">
-        <v>0.8252047759581963</v>
+        <v>0.8264006388339326</v>
       </c>
       <c r="F97">
-        <v>4.179049171530583</v>
+        <v>3.781357362460543</v>
       </c>
       <c r="G97">
-        <v>154.2686987131546</v>
+        <v>204.5987623370494</v>
       </c>
       <c r="H97">
-        <v>644.1790485643262</v>
+        <v>777.8155627410831</v>
       </c>
       <c r="I97">
-        <v>2408.426785128595</v>
+        <v>2564.834021749035</v>
       </c>
       <c r="J97">
-        <v>25.92829976365709</v>
+        <v>33.82687089245699</v>
       </c>
       <c r="K97">
-        <v>129.4925814606805</v>
+        <v>167.5599260160454</v>
       </c>
       <c r="L97">
-        <v>551.5472491363031</v>
+        <v>655.6806093244622</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4101,37 +4101,37 @@
         <v>96</v>
       </c>
       <c r="B98">
-        <v>5284.535045917548</v>
+        <v>17421.15954620184</v>
       </c>
       <c r="C98">
-        <v>981.9359999460876</v>
+        <v>3360.322025718969</v>
       </c>
       <c r="D98">
-        <v>0.1858131304672983</v>
+        <v>0.1928873917265505</v>
       </c>
       <c r="E98">
-        <v>0.8141868695327017</v>
+        <v>0.8071126082734495</v>
       </c>
       <c r="F98">
-        <v>3.958346920324851</v>
+        <v>3.470661696354207</v>
       </c>
       <c r="G98">
-        <v>122.40698746053</v>
+        <v>161.0290932380663</v>
       </c>
       <c r="H98">
-        <v>489.9103498511716</v>
+        <v>573.2168004040336</v>
       </c>
       <c r="I98">
-        <v>1764.247736564269</v>
+        <v>1787.018459007952</v>
       </c>
       <c r="J98">
-        <v>21.87002454914655</v>
+        <v>29.58141122550677</v>
       </c>
       <c r="K98">
-        <v>103.5642816970234</v>
+        <v>133.7330551235884</v>
       </c>
       <c r="L98">
-        <v>422.0546676756227</v>
+        <v>488.1206833084167</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4139,37 +4139,37 @@
         <v>97</v>
       </c>
       <c r="B99">
-        <v>4302.59904597146</v>
+        <v>14060.83752048288</v>
       </c>
       <c r="C99">
-        <v>849.5026878814019</v>
+        <v>3009.445076195057</v>
       </c>
       <c r="D99">
-        <v>0.1974394264501115</v>
+        <v>0.2140302860203812</v>
       </c>
       <c r="E99">
-        <v>0.8025605735498885</v>
+        <v>0.7859697139796188</v>
       </c>
       <c r="F99">
-        <v>3.747608319094793</v>
+        <v>3.180603754547901</v>
       </c>
       <c r="G99">
-        <v>95.82900185520921</v>
+        <v>123.779629953604</v>
       </c>
       <c r="H99">
-        <v>367.5033623906417</v>
+        <v>412.1877071659674</v>
       </c>
       <c r="I99">
-        <v>1274.337386713098</v>
+        <v>1213.801658603918</v>
       </c>
       <c r="J99">
-        <v>18.19271458036459</v>
+        <v>25.23103771663505</v>
       </c>
       <c r="K99">
-        <v>81.69425714787681</v>
+        <v>104.1516438980817</v>
       </c>
       <c r="L99">
-        <v>318.4903859785993</v>
+        <v>354.3876281848284</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4177,37 +4177,37 @@
         <v>98</v>
       </c>
       <c r="B100">
-        <v>3453.096358090058</v>
+        <v>11051.39244428782</v>
       </c>
       <c r="C100">
-        <v>724.0996876412266</v>
+        <v>2620.666323890309</v>
       </c>
       <c r="D100">
-        <v>0.2096957665096069</v>
+        <v>0.2371344911604206</v>
       </c>
       <c r="E100">
-        <v>0.7903042334903931</v>
+        <v>0.7628655088395794</v>
       </c>
       <c r="F100">
-        <v>3.546558510505894</v>
+        <v>2.910568762217487</v>
       </c>
       <c r="G100">
-        <v>73.95055643425965</v>
+        <v>92.65432414394016</v>
       </c>
       <c r="H100">
-        <v>271.6743605354324</v>
+        <v>288.4080772123634</v>
       </c>
       <c r="I100">
-        <v>906.8340243224561</v>
+        <v>801.6139514379511</v>
       </c>
       <c r="J100">
-        <v>14.91069097624425</v>
+        <v>20.92527239017706</v>
       </c>
       <c r="K100">
-        <v>63.50154256751222</v>
+        <v>78.92060618144663</v>
       </c>
       <c r="L100">
-        <v>236.7961288307225</v>
+        <v>250.2359842867467</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4215,37 +4215,37 @@
         <v>99</v>
       </c>
       <c r="B101">
-        <v>2728.996670448832</v>
+        <v>8430.726120397509</v>
       </c>
       <c r="C101">
-        <v>607.4824077827107</v>
+        <v>2211.328002702248</v>
       </c>
       <c r="D101">
-        <v>0.2226028394834206</v>
+        <v>0.2622938962934765</v>
       </c>
       <c r="E101">
-        <v>0.7773971605165794</v>
+        <v>0.7377061037065235</v>
       </c>
       <c r="F101">
-        <v>3.354918626780868</v>
+        <v>2.659886945058356</v>
       </c>
       <c r="G101">
-        <v>56.19561328746695</v>
+        <v>67.3169410802421</v>
       </c>
       <c r="H101">
-        <v>197.7238041011728</v>
+        <v>195.7537530684232</v>
       </c>
       <c r="I101">
-        <v>635.1596637870236</v>
+        <v>513.2058742255876</v>
       </c>
       <c r="J101">
-        <v>12.02817604259845</v>
+        <v>16.81602167856676</v>
       </c>
       <c r="K101">
-        <v>48.59085159126798</v>
+        <v>57.99533379126957</v>
       </c>
       <c r="L101">
-        <v>173.2945862632103</v>
+        <v>171.3153781053</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4253,37 +4253,37 @@
         <v>100</v>
       </c>
       <c r="B102">
-        <v>2121.514262666121</v>
+        <v>6219.39811769526</v>
       </c>
       <c r="C102">
-        <v>501.0593477077775</v>
+        <v>1801.03788958882</v>
       </c>
       <c r="D102">
-        <v>0.2361800514497098</v>
+        <v>0.2895839525796807</v>
       </c>
       <c r="E102">
-        <v>0.7638199485502902</v>
+        <v>0.7104160474203193</v>
       </c>
       <c r="F102">
-        <v>3.172406810546849</v>
+        <v>2.427842041981545</v>
       </c>
       <c r="G102">
-        <v>42.00606750304284</v>
+        <v>47.29535077880668</v>
       </c>
       <c r="H102">
-        <v>141.5281908137058</v>
+        <v>128.4368119881811</v>
       </c>
       <c r="I102">
-        <v>437.435859685851</v>
+        <v>317.4521211571644</v>
       </c>
       <c r="J102">
-        <v>9.539418446219846</v>
+        <v>13.04378534968506</v>
       </c>
       <c r="K102">
-        <v>36.56267554866953</v>
+        <v>41.17931211270281</v>
       </c>
       <c r="L102">
-        <v>124.7037346719423</v>
+        <v>113.3200443140304</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4291,37 +4291,37 @@
         <v>101</v>
       </c>
       <c r="B103">
-        <v>1620.454914958343</v>
+        <v>4418.36022810644</v>
       </c>
       <c r="C103">
-        <v>405.835108403661</v>
+        <v>1409.698828615678</v>
       </c>
       <c r="D103">
-        <v>0.2504451710796864</v>
+        <v>0.3190547524052441</v>
       </c>
       <c r="E103">
-        <v>0.7495548289203136</v>
+        <v>0.6809452475947559</v>
       </c>
       <c r="F103">
-        <v>2.998739219391961</v>
+        <v>2.213680313081291</v>
       </c>
       <c r="G103">
-        <v>30.85103107593673</v>
+        <v>31.99940586822605</v>
       </c>
       <c r="H103">
-        <v>99.52212331066299</v>
+        <v>81.14146120937447</v>
       </c>
       <c r="I103">
-        <v>295.9076688721452</v>
+        <v>189.0153091689832</v>
       </c>
       <c r="J103">
-        <v>7.429318995959322</v>
+        <v>9.723392872763597</v>
       </c>
       <c r="K103">
-        <v>27.02325710244968</v>
+        <v>28.13552676301774</v>
       </c>
       <c r="L103">
-        <v>88.14105912327274</v>
+        <v>72.14073220132764</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4329,37 +4329,37 @@
         <v>102</v>
       </c>
       <c r="B104">
-        <v>1214.619806554682</v>
+        <v>3008.661399490763</v>
       </c>
       <c r="C104">
-        <v>322.3770237636083</v>
+        <v>1055.207048640793</v>
       </c>
       <c r="D104">
-        <v>0.2654139361336809</v>
+        <v>0.350723098591086</v>
       </c>
       <c r="E104">
-        <v>0.7345860638663191</v>
+        <v>0.649276901408914</v>
       </c>
       <c r="F104">
-        <v>2.833631007342368</v>
+        <v>2.016619829765133</v>
       </c>
       <c r="G104">
-        <v>22.23513396167214</v>
+        <v>20.75223176364217</v>
       </c>
       <c r="H104">
-        <v>68.67109223472625</v>
+        <v>49.14205534114841</v>
       </c>
       <c r="I104">
-        <v>196.3855455614822</v>
+        <v>107.8738479596088</v>
       </c>
       <c r="J104">
-        <v>5.674533101179895</v>
+        <v>6.931701930309464</v>
       </c>
       <c r="K104">
-        <v>19.59393810649036</v>
+        <v>18.41213389025415</v>
       </c>
       <c r="L104">
-        <v>61.11780202082309</v>
+        <v>44.00520543830989</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4367,37 +4367,37 @@
         <v>103</v>
       </c>
       <c r="B105">
-        <v>892.242782791074</v>
+        <v>1953.454350849969</v>
       </c>
       <c r="C105">
-        <v>250.8091075737486</v>
+        <v>751.2276164020647</v>
       </c>
       <c r="D105">
-        <v>0.2810996204297431</v>
+        <v>0.3845636915319763</v>
       </c>
       <c r="E105">
-        <v>0.7189003795702569</v>
+        <v>0.6154363084680237</v>
       </c>
       <c r="F105">
-        <v>2.676797276904296</v>
+        <v>1.835859825713971</v>
       </c>
       <c r="G105">
-        <v>15.70540340042794</v>
+        <v>12.83232832077831</v>
       </c>
       <c r="H105">
-        <v>46.43595827305411</v>
+        <v>28.38982357750624</v>
       </c>
       <c r="I105">
-        <v>127.7144533267559</v>
+        <v>58.73179261846036</v>
       </c>
       <c r="J105">
-        <v>4.244983590919508</v>
+        <v>4.699854809513177</v>
       </c>
       <c r="K105">
-        <v>13.91940500531046</v>
+        <v>11.48043195994468</v>
       </c>
       <c r="L105">
-        <v>41.52386391433273</v>
+        <v>25.59307154805574</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4405,37 +4405,37 @@
         <v>104</v>
       </c>
       <c r="B106">
-        <v>641.4336752173253</v>
+        <v>1202.226734447905</v>
       </c>
       <c r="C106">
-        <v>190.8345756932468</v>
+        <v>505.5359762712267</v>
       </c>
       <c r="D106">
-        <v>0.2975125614173434</v>
+        <v>0.4204996959274763</v>
       </c>
       <c r="E106">
-        <v>0.7024874385826566</v>
+        <v>0.5795003040725237</v>
       </c>
       <c r="F106">
-        <v>2.527953995803338</v>
+        <v>1.670589884498793</v>
       </c>
       <c r="G106">
-        <v>10.85636583256889</v>
+        <v>7.521410257894741</v>
       </c>
       <c r="H106">
-        <v>30.73055487262619</v>
+        <v>15.55749525672792</v>
       </c>
       <c r="I106">
-        <v>81.27849505370179</v>
+        <v>30.34196904095412</v>
       </c>
       <c r="J106">
-        <v>3.105678083203173</v>
+        <v>3.012143548943371</v>
       </c>
       <c r="K106">
-        <v>9.674421414390956</v>
+        <v>6.780577150431506</v>
       </c>
       <c r="L106">
-        <v>27.60445890902226</v>
+        <v>14.11263958811106</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4443,37 +4443,37 @@
         <v>105</v>
       </c>
       <c r="B107">
-        <v>450.5990995240786</v>
+        <v>696.6907581766779</v>
       </c>
       <c r="C107">
-        <v>141.7853547246312</v>
+        <v>319.358252001969</v>
       </c>
       <c r="D107">
-        <v>0.3146596495074768</v>
+        <v>0.4583931224202935</v>
       </c>
       <c r="E107">
-        <v>0.6853403504925232</v>
+        <v>0.5416068775797065</v>
       </c>
       <c r="F107">
-        <v>2.386818873081847</v>
+        <v>1.519998740763896</v>
       </c>
       <c r="G107">
-        <v>7.333135217343836</v>
+        <v>4.151104315718287</v>
       </c>
       <c r="H107">
-        <v>19.87418904005729</v>
+        <v>8.036084998833182</v>
       </c>
       <c r="I107">
-        <v>50.54794018107561</v>
+        <v>14.7844737842262</v>
       </c>
       <c r="J107">
-        <v>2.218693997384948</v>
+        <v>1.812226351213773</v>
       </c>
       <c r="K107">
-        <v>6.568743331187783</v>
+        <v>3.768433601488135</v>
       </c>
       <c r="L107">
-        <v>17.9300374946313</v>
+        <v>7.332062437679552</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4481,37 +4481,37 @@
         <v>106</v>
       </c>
       <c r="B108">
-        <v>308.8137447994473</v>
+        <v>377.3325061747089</v>
       </c>
       <c r="C108">
-        <v>102.694090496799</v>
+        <v>187.9250482328983</v>
       </c>
       <c r="D108">
-        <v>0.3325437815712885</v>
+        <v>0.4980356718747339</v>
       </c>
       <c r="E108">
-        <v>0.6674562184287115</v>
+        <v>0.5019643281252661</v>
       </c>
       <c r="F108">
-        <v>2.253112189769471</v>
+        <v>1.383282474775787</v>
       </c>
       <c r="G108">
-        <v>4.832397557753355</v>
+        <v>2.141206330422691</v>
       </c>
       <c r="H108">
-        <v>12.54105382271346</v>
+        <v>3.884980683114895</v>
       </c>
       <c r="I108">
-        <v>30.67375114101833</v>
+        <v>6.748388785393018</v>
       </c>
       <c r="J108">
-        <v>1.545176690299192</v>
+        <v>1.01561631751857</v>
       </c>
       <c r="K108">
-        <v>4.350049333802836</v>
+        <v>1.956207250274362</v>
       </c>
       <c r="L108">
-        <v>11.36129416344352</v>
+        <v>3.563628836191417</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4519,37 +4519,37 @@
         <v>107</v>
       </c>
       <c r="B109">
-        <v>206.1196543026483</v>
+        <v>189.4074579418106</v>
       </c>
       <c r="C109">
-        <v>72.38165440235987</v>
+        <v>102.117313465306</v>
       </c>
       <c r="D109">
-        <v>0.3511632825469467</v>
+        <v>0.5391409323315997</v>
       </c>
       <c r="E109">
-        <v>0.6488367174530533</v>
+        <v>0.4608590676684003</v>
       </c>
       <c r="F109">
-        <v>2.126557579906215</v>
+        <v>1.259651882185864</v>
       </c>
       <c r="G109">
-        <v>3.101359422925187</v>
+        <v>1.023627806693517</v>
       </c>
       <c r="H109">
-        <v>7.708656264960101</v>
+        <v>1.743774352692203</v>
       </c>
       <c r="I109">
-        <v>18.13269731830487</v>
+        <v>2.863408102278124</v>
       </c>
       <c r="J109">
-        <v>1.04719572626184</v>
+        <v>0.5255996667250409</v>
       </c>
       <c r="K109">
-        <v>2.804872643503644</v>
+        <v>0.9405909327557924</v>
       </c>
       <c r="L109">
-        <v>7.011244829640681</v>
+        <v>1.607421585917054</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4557,37 +4557,37 @@
         <v>108</v>
       </c>
       <c r="B110">
-        <v>133.7379999002884</v>
+        <v>87.29014447650458</v>
       </c>
       <c r="C110">
-        <v>49.55144032404993</v>
+        <v>50.74517144410657</v>
       </c>
       <c r="D110">
-        <v>0.370511300909197</v>
+        <v>0.5813390703891592</v>
       </c>
       <c r="E110">
-        <v>0.629488699090803</v>
+        <v>0.4186609296108408</v>
       </c>
       <c r="F110">
-        <v>2.006882758255593</v>
+        <v>1.148338799167237</v>
       </c>
       <c r="G110">
-        <v>1.934880641935456</v>
+        <v>0.4492839586973558</v>
       </c>
       <c r="H110">
-        <v>4.607296842034915</v>
+        <v>0.7201465459986865</v>
       </c>
       <c r="I110">
-        <v>10.42404105334477</v>
+        <v>1.119633749585921</v>
       </c>
       <c r="J110">
-        <v>0.6893222536033922</v>
+        <v>0.2487488751332212</v>
       </c>
       <c r="K110">
-        <v>1.757676917241805</v>
+        <v>0.4149912660307516</v>
       </c>
       <c r="L110">
-        <v>4.206372186137037</v>
+        <v>0.6668306531612617</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4595,37 +4595,37 @@
         <v>109</v>
       </c>
       <c r="B111">
-        <v>84.18655957623849</v>
+        <v>36.544973032398</v>
       </c>
       <c r="C111">
-        <v>32.88118115431447</v>
+        <v>22.8104725649766</v>
       </c>
       <c r="D111">
-        <v>0.3905751858708231</v>
+        <v>0.6241753837047455</v>
       </c>
       <c r="E111">
-        <v>0.6094248141291769</v>
+        <v>0.3758246162952545</v>
       </c>
       <c r="F111">
-        <v>1.893820191580956</v>
+        <v>1.048601155044226</v>
       </c>
       <c r="G111">
-        <v>1.171139902103776</v>
+        <v>0.179140609340451</v>
       </c>
       <c r="H111">
-        <v>2.672416200099458</v>
+        <v>0.2708625873013307</v>
       </c>
       <c r="I111">
-        <v>5.816744211309853</v>
+        <v>0.3994872035872343</v>
       </c>
       <c r="J111">
-        <v>0.4398251778316538</v>
+        <v>0.106490627211598</v>
       </c>
       <c r="K111">
-        <v>1.068354663638412</v>
+        <v>0.1662423908975305</v>
       </c>
       <c r="L111">
-        <v>2.448695268895232</v>
+        <v>0.25183938713051</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4633,37 +4633,37 @@
         <v>110</v>
       </c>
       <c r="B112">
-        <v>51.30537842192403</v>
+        <v>13.73450046742141</v>
       </c>
       <c r="C112">
-        <v>21.10374178148575</v>
+        <v>9.162480626789653</v>
       </c>
       <c r="D112">
-        <v>0.4113358566022702</v>
+        <v>0.6671142243959507</v>
       </c>
       <c r="E112">
-        <v>0.5886641433977298</v>
+        <v>0.3328857756040493</v>
       </c>
       <c r="F112">
-        <v>1.787107710854574</v>
+        <v>0.9597265087426701</v>
       </c>
       <c r="G112">
-        <v>0.6862708818835158</v>
+        <v>0.06411947692216484</v>
       </c>
       <c r="H112">
-        <v>1.501276297995682</v>
+        <v>0.09172197796087972</v>
       </c>
       <c r="I112">
-        <v>3.144328011210395</v>
+        <v>0.1286246162859036</v>
       </c>
       <c r="J112">
-        <v>0.2714305971737994</v>
+        <v>0.04073810963390864</v>
       </c>
       <c r="K112">
-        <v>0.6285294858067586</v>
+        <v>0.05975176368593249</v>
       </c>
       <c r="L112">
-        <v>1.38034060525682</v>
+        <v>0.08559699623297956</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -4671,37 +4671,37 @@
         <v>111</v>
       </c>
       <c r="B113">
-        <v>30.20163664043827</v>
+        <v>4.572019840631752</v>
       </c>
       <c r="C113">
-        <v>13.07027701340797</v>
+        <v>3.244075717349274</v>
       </c>
       <c r="D113">
-        <v>0.4327671764618085</v>
+        <v>0.7095497899022709</v>
       </c>
       <c r="E113">
-        <v>0.5672328235381915</v>
+        <v>0.2904502100977291</v>
       </c>
       <c r="F113">
-        <v>1.686489062210372</v>
+        <v>0.8810338032872012</v>
       </c>
       <c r="G113">
-        <v>0.3884452507911196</v>
+        <v>0.02032805886339122</v>
       </c>
       <c r="H113">
-        <v>0.8150054161121661</v>
+        <v>0.02760250103871487</v>
       </c>
       <c r="I113">
-        <v>1.643051713214713</v>
+        <v>0.03690263832502386</v>
       </c>
       <c r="J113">
-        <v>0.1616407253796845</v>
+        <v>0.01373692371013356</v>
       </c>
       <c r="K113">
-        <v>0.3570988886329594</v>
+        <v>0.01901365405202385</v>
       </c>
       <c r="L113">
-        <v>0.7518111194500617</v>
+        <v>0.02584523254704706</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -4709,37 +4709,37 @@
         <v>112</v>
       </c>
       <c r="B114">
-        <v>17.1313596270303</v>
+        <v>1.327944123282478</v>
       </c>
       <c r="C114">
-        <v>7.791947920935902</v>
+        <v>0.9970536724544408</v>
       </c>
       <c r="D114">
-        <v>0.4548353481904358</v>
+        <v>0.7508250196475692</v>
       </c>
       <c r="E114">
-        <v>0.5451646518095642</v>
+        <v>0.2491749803524308</v>
       </c>
       <c r="F114">
-        <v>1.591714394822016</v>
+        <v>0.8118730510093036</v>
       </c>
       <c r="G114">
-        <v>0.2118643234579305</v>
+        <v>0.005623132350239033</v>
       </c>
       <c r="H114">
-        <v>0.4265601653210466</v>
+        <v>0.007274442175323642</v>
       </c>
       <c r="I114">
-        <v>0.8280462971025466</v>
+        <v>0.009300137286308989</v>
       </c>
       <c r="J114">
-        <v>0.09265709935492203</v>
+        <v>0.004020941387951527</v>
       </c>
       <c r="K114">
-        <v>0.1954581632532748</v>
+        <v>0.005276730341890288</v>
       </c>
       <c r="L114">
-        <v>0.3947122308171024</v>
+        <v>0.006831578495023214</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -4747,37 +4747,37 @@
         <v>113</v>
       </c>
       <c r="B115">
-        <v>9.339411706094401</v>
+        <v>0.3308904508280375</v>
       </c>
       <c r="C115">
-        <v>4.459553672007787</v>
+        <v>0.2614892373852673</v>
       </c>
       <c r="D115">
-        <v>0.4774983491837843</v>
+        <v>0.7902592435983058</v>
       </c>
       <c r="E115">
-        <v>0.5225016508162157</v>
+        <v>0.2097407564016942</v>
       </c>
       <c r="F115">
-        <v>1.502540684173653</v>
+        <v>0.7516226571712508</v>
       </c>
       <c r="G115">
-        <v>0.1110585962777034</v>
+        <v>0.001334422755133266</v>
       </c>
       <c r="H115">
-        <v>0.2146958418631161</v>
+        <v>0.001651309825084609</v>
       </c>
       <c r="I115">
-        <v>0.4014861317815001</v>
+        <v>0.002025695110985348</v>
       </c>
       <c r="J115">
-        <v>0.05099066960122282</v>
+        <v>0.00100432373058284</v>
       </c>
       <c r="K115">
-        <v>0.1028010638983528</v>
+        <v>0.00125578895393876</v>
       </c>
       <c r="L115">
-        <v>0.1992540675638276</v>
+        <v>0.001554848153132925</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -4785,37 +4785,37 @@
         <v>114</v>
       </c>
       <c r="B116">
-        <v>4.879858034086614</v>
+        <v>0.06940121344277018</v>
       </c>
       <c r="C116">
-        <v>2.44337141147017</v>
+        <v>0.05740758992067914</v>
       </c>
       <c r="D116">
-        <v>0.5007054292159356</v>
+        <v>0.8271842389041042</v>
       </c>
       <c r="E116">
-        <v>0.4992945707840644</v>
+        <v>0.1728157610958958</v>
       </c>
       <c r="F116">
-        <v>1.418732089377237</v>
+        <v>0.6996841314395974</v>
       </c>
       <c r="G116">
-        <v>0.0557964422042612</v>
+        <v>0.0002665550838297942</v>
       </c>
       <c r="H116">
-        <v>0.1036372455854127</v>
+        <v>0.0003168870699513432</v>
       </c>
       <c r="I116">
-        <v>0.1867902899183839</v>
+        <v>0.0003743852859007389</v>
       </c>
       <c r="J116">
-        <v>0.02686305917558341</v>
+        <v>0.0002099906325178743</v>
       </c>
       <c r="K116">
-        <v>0.05181039429712994</v>
+        <v>0.0002514652233559207</v>
       </c>
       <c r="L116">
-        <v>0.09645300366547487</v>
+        <v>0.0002990591991941651</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -4823,37 +4823,37 @@
         <v>115</v>
       </c>
       <c r="B117">
-        <v>2.436486622616444</v>
+        <v>0.01199362352209104</v>
       </c>
       <c r="C117">
-        <v>1.277685535301723</v>
+        <v>0.01032635349284631</v>
       </c>
       <c r="D117">
-        <v>0.5243966962271553</v>
+        <v>0.8609869630997011</v>
       </c>
       <c r="E117">
-        <v>0.4756033037728447</v>
+        <v>0.1390130369002989</v>
       </c>
       <c r="F117">
-        <v>1.340060243263834</v>
+        <v>0.6554740735064797</v>
       </c>
       <c r="G117">
-        <v>0.02678736602082158</v>
+        <v>4.387135208192971E-05</v>
       </c>
       <c r="H117">
-        <v>0.04784080338115151</v>
+        <v>5.0331986121549E-05</v>
       </c>
       <c r="I117">
-        <v>0.0831530443329712</v>
+        <v>5.749821594939561E-05</v>
       </c>
       <c r="J117">
-        <v>0.01350692907879462</v>
+        <v>3.597396399628419E-05</v>
       </c>
       <c r="K117">
-        <v>0.02494733512154652</v>
+        <v>4.147459083804641E-05</v>
       </c>
       <c r="L117">
-        <v>0.04464260936834492</v>
+        <v>4.759397583824444E-05</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -4861,37 +4861,37 @@
         <v>116</v>
       </c>
       <c r="B118">
-        <v>1.158801087314721</v>
+        <v>0.001667270029244735</v>
       </c>
       <c r="C118">
-        <v>0.6356056628492537</v>
+        <v>0.001485796950216175</v>
       </c>
       <c r="D118">
-        <v>0.5485028188247016</v>
+        <v>0.8911555561814026</v>
       </c>
       <c r="E118">
-        <v>0.4514971811752984</v>
+        <v>0.1088444438185974</v>
       </c>
       <c r="F118">
-        <v>1.26630447391732</v>
+        <v>0.6184136176953448</v>
       </c>
       <c r="G118">
-        <v>0.01225015363353383</v>
+        <v>5.808276081744093E-06</v>
       </c>
       <c r="H118">
-        <v>0.02105343736032993</v>
+        <v>6.460634039619294E-06</v>
       </c>
       <c r="I118">
-        <v>0.0353122409518197</v>
+        <v>7.166229827846611E-06</v>
       </c>
       <c r="J118">
-        <v>0.00646081134522016</v>
+        <v>4.929597621030281E-06</v>
       </c>
       <c r="K118">
-        <v>0.01144040604275191</v>
+        <v>5.500626841762222E-06</v>
       </c>
       <c r="L118">
-        <v>0.01969527424679839</v>
+        <v>6.119385000198026E-06</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -4899,37 +4899,37 @@
         <v>117</v>
       </c>
       <c r="B119">
-        <v>0.5231954244654673</v>
+        <v>0.0001814730790285597</v>
       </c>
       <c r="C119">
-        <v>0.2997621379916046</v>
+        <v>0.0001664695198096652</v>
       </c>
       <c r="D119">
-        <v>0.5729448767596972</v>
+        <v>0.9173234988946578</v>
       </c>
       <c r="E119">
-        <v>0.4270551232403028</v>
+        <v>0.08267650110534219</v>
       </c>
       <c r="F119">
-        <v>1.197251956086509</v>
+        <v>0.5879160528643574</v>
       </c>
       <c r="G119">
-        <v>0.005318182533177752</v>
+        <v>6.020938853926645E-07</v>
       </c>
       <c r="H119">
-        <v>0.008803283726796094</v>
+        <v>6.523579578752001E-07</v>
       </c>
       <c r="I119">
-        <v>0.01425880359148977</v>
+        <v>7.055957882273174E-07</v>
       </c>
       <c r="J119">
-        <v>0.002929832150054905</v>
+        <v>5.26014161534741E-07</v>
       </c>
       <c r="K119">
-        <v>0.004979594697531749</v>
+        <v>5.710292207319407E-07</v>
       </c>
       <c r="L119">
-        <v>0.008254868204046488</v>
+        <v>6.18758158435804E-07</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -4937,37 +4937,37 @@
         <v>118</v>
       </c>
       <c r="B120">
-        <v>0.2234332864738627</v>
+        <v>1.500355921889457E-05</v>
       </c>
       <c r="C120">
-        <v>0.1335314164392539</v>
+        <v>1.409292574131231E-05</v>
       </c>
       <c r="D120">
-        <v>0.5976343925589369</v>
+        <v>0.9393055031611787</v>
       </c>
       <c r="E120">
-        <v>0.4023656074410631</v>
+        <v>0.06069449683882133</v>
       </c>
       <c r="F120">
-        <v>1.132697790383766</v>
+        <v>0.563374135201238</v>
       </c>
       <c r="G120">
-        <v>0.002183804901077549</v>
+        <v>4.740858645827276E-08</v>
       </c>
       <c r="H120">
-        <v>0.003485101193618342</v>
+        <v>5.026407248253555E-08</v>
       </c>
       <c r="I120">
-        <v>0.00545551986469368</v>
+        <v>5.323783035211734E-08</v>
       </c>
       <c r="J120">
-        <v>0.001254920111079529</v>
+        <v>4.241061538795061E-08</v>
       </c>
       <c r="K120">
-        <v>0.002049762547476843</v>
+        <v>4.501505919719964E-08</v>
       </c>
       <c r="L120">
-        <v>0.003275273506514738</v>
+        <v>4.772893770386329E-08</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -4975,37 +4975,37 @@
         <v>119</v>
       </c>
       <c r="B121">
-        <v>0.08990187003460882</v>
+        <v>9.106334775822652E-07</v>
       </c>
       <c r="C121">
-        <v>0.05596153874382179</v>
+        <v>8.715839944054233E-07</v>
       </c>
       <c r="D121">
-        <v>0.6224735783836166</v>
+        <v>0.9571183312077233</v>
       </c>
       <c r="E121">
-        <v>0.3775264216163834</v>
+        <v>0.04288166879227673</v>
       </c>
       <c r="F121">
-        <v>1.072445006936736</v>
+        <v>0.5441496099643551</v>
       </c>
       <c r="G121">
-        <v>0.0008448922938027294</v>
+        <v>2.740419334213928E-09</v>
       </c>
       <c r="H121">
-        <v>0.001301296292540793</v>
+        <v>2.855486024262784E-09</v>
       </c>
       <c r="I121">
-        <v>0.00197041867107534</v>
+        <v>2.973757869581788E-09</v>
       </c>
       <c r="J121">
-        <v>0.000505695316800122</v>
+        <v>2.498005314259252E-09</v>
       </c>
       <c r="K121">
-        <v>0.0007948424363973141</v>
+        <v>2.604443809249033E-09</v>
       </c>
       <c r="L121">
-        <v>0.001225510959037895</v>
+        <v>2.713878506663651E-09</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5013,37 +5013,37 @@
         <v>120</v>
       </c>
       <c r="B122">
-        <v>0.03394033129078704</v>
+        <v>3.904948317684185E-08</v>
       </c>
       <c r="C122">
-        <v>0.02197147139053067</v>
+        <v>3.791629899364383E-08</v>
       </c>
       <c r="D122">
-        <v>0.6473558316885001</v>
+        <v>0.9709808148275302</v>
       </c>
       <c r="E122">
-        <v>0.3526441683114999</v>
+        <v>0.02901918517246982</v>
       </c>
       <c r="F122">
-        <v>1.016304486678857</v>
+        <v>0.5295683728686125</v>
       </c>
       <c r="G122">
-        <v>0.0003067011195486562</v>
+        <v>1.11917861182584E-10</v>
       </c>
       <c r="H122">
-        <v>0.0004564039987380636</v>
+        <v>1.150666900488561E-10</v>
       </c>
       <c r="I122">
-        <v>0.000669122378534546</v>
+        <v>1.182718453190044E-10</v>
       </c>
       <c r="J122">
-        <v>0.0001909084214665524</v>
+        <v>1.03495329566495E-10</v>
       </c>
       <c r="K122">
-        <v>0.0002891471195971922</v>
+        <v>1.064384949897813E-10</v>
       </c>
       <c r="L122">
-        <v>0.000430668522640581</v>
+        <v>1.094346974146178E-10</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5051,37 +5051,37 @@
         <v>121</v>
       </c>
       <c r="B123">
-        <v>0.01196885990025637</v>
+        <v>1.133184183198019E-09</v>
       </c>
       <c r="C123">
-        <v>0.008045066799387993</v>
+        <v>1.111982490674401E-09</v>
       </c>
       <c r="D123">
-        <v>0.672166510965315</v>
+        <v>0.9812901619719194</v>
       </c>
       <c r="E123">
-        <v>0.327833489034685</v>
+        <v>0.01870983802808057</v>
       </c>
       <c r="F123">
-        <v>0.9640947818617868</v>
+        <v>0.5189249867933473</v>
       </c>
       <c r="G123">
-        <v>0.0001039965011763863</v>
+        <v>3.0931096550135E-12</v>
       </c>
       <c r="H123">
-        <v>0.0001497028791894074</v>
+        <v>3.148828866272188E-12</v>
       </c>
       <c r="I123">
-        <v>0.0002127183797964825</v>
+        <v>3.205155270148273E-12</v>
       </c>
       <c r="J123">
-        <v>6.721438975801141E-05</v>
+        <v>2.890702927966767E-12</v>
       </c>
       <c r="K123">
-        <v>9.823869813063988E-05</v>
+        <v>2.943165423286253E-12</v>
       </c>
       <c r="L123">
-        <v>0.0001415214030433888</v>
+        <v>2.996202424836555E-12</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5089,37 +5089,37 @@
         <v>122</v>
       </c>
       <c r="B124">
-        <v>0.003923793100868378</v>
+        <v>2.120169252361771E-11</v>
       </c>
       <c r="C124">
-        <v>0.00273403632405266</v>
+        <v>2.095948418501194E-11</v>
       </c>
       <c r="D124">
-        <v>0.696784018364166</v>
+        <v>0.9885759904151068</v>
       </c>
       <c r="E124">
-        <v>0.303215981635834</v>
+        <v>0.0114240095848932</v>
       </c>
       <c r="F124">
-        <v>0.9156417735977097</v>
+        <v>0.5114992318449679</v>
       </c>
       <c r="G124">
-        <v>3.278224598851389E-05</v>
+        <v>5.511579109370929E-14</v>
       </c>
       <c r="H124">
-        <v>4.570637801302106E-05</v>
+        <v>5.571921125868718E-14</v>
       </c>
       <c r="I124">
-        <v>6.301550060707506E-05</v>
+        <v>5.632640387608507E-14</v>
       </c>
       <c r="J124">
-        <v>2.196360104892237E-05</v>
+        <v>5.189156930283407E-14</v>
       </c>
       <c r="K124">
-        <v>3.102430837262845E-05</v>
+        <v>5.246249531948609E-14</v>
       </c>
       <c r="L124">
-        <v>4.328270491274892E-05</v>
+        <v>5.303700155030216E-14</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5127,37 +5127,37 @@
         <v>123</v>
       </c>
       <c r="B125">
-        <v>0.001189756776815718</v>
+        <v>2.422083386057672E-13</v>
       </c>
       <c r="C125">
-        <v>0.000857911254935346</v>
+        <v>2.406191003953305E-13</v>
       </c>
       <c r="D125">
-        <v>0.7210812089101706</v>
+        <v>0.9934385487321165</v>
       </c>
       <c r="E125">
-        <v>0.2789187910898294</v>
+        <v>0.006561451267883545</v>
       </c>
       <c r="F125">
-        <v>0.870777923232623</v>
+        <v>0.5065845760646212</v>
       </c>
       <c r="G125">
-        <v>9.557789324648672E-06</v>
+        <v>5.996603102223869E-16</v>
       </c>
       <c r="H125">
-        <v>1.292413202450717E-05</v>
+        <v>6.034201649778816E-16</v>
       </c>
       <c r="I125">
-        <v>1.7309122594054E-05</v>
+        <v>6.071926173978976E-16</v>
       </c>
       <c r="J125">
-        <v>6.626867577621525E-06</v>
+        <v>5.673577793519799E-16</v>
       </c>
       <c r="K125">
-        <v>9.060707323706087E-06</v>
+        <v>5.709260166520116E-16</v>
       </c>
       <c r="L125">
-        <v>1.225839654012047E-05</v>
+        <v>5.745062308160769E-16</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5165,37 +5165,37 @@
         <v>124</v>
       </c>
       <c r="B126">
-        <v>0.0003318455218803721</v>
+        <v>1.589238210436778E-15</v>
       </c>
       <c r="C126">
-        <v>0.0002472007342250149</v>
+        <v>1.583646962613378E-15</v>
       </c>
       <c r="D126">
-        <v>0.7449271360489503</v>
+        <v>0.9964818063228775</v>
       </c>
       <c r="E126">
-        <v>0.2550728639510497</v>
+        <v>0.003518193677122472</v>
       </c>
       <c r="F126">
-        <v>0.8293400626894629</v>
+        <v>0.5035243417642672</v>
       </c>
       <c r="G126">
-        <v>2.563314465309889E-06</v>
+        <v>3.7472780026744E-18</v>
       </c>
       <c r="H126">
-        <v>3.366342699858495E-06</v>
+        <v>3.759854755494721E-18</v>
       </c>
       <c r="I126">
-        <v>4.384990569546831E-06</v>
+        <v>3.772452420015899E-18</v>
       </c>
       <c r="J126">
-        <v>1.836040868688598E-06</v>
+        <v>3.556280336094258E-18</v>
       </c>
       <c r="K126">
-        <v>2.433839746084562E-06</v>
+        <v>3.568237300031795E-18</v>
       </c>
       <c r="L126">
-        <v>3.197689216414385E-06</v>
+        <v>3.580214164065393E-18</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5203,37 +5203,37 @@
         <v>125</v>
       </c>
       <c r="B127">
-        <v>8.464478765535722E-05</v>
+        <v>5.591247823400106E-18</v>
       </c>
       <c r="C127">
-        <v>6.502320580192157E-05</v>
+        <v>5.5814848078361E-18</v>
       </c>
       <c r="D127">
-        <v>0.7681891301644279</v>
+        <v>0.9982538753651472</v>
       </c>
       <c r="E127">
-        <v>0.2318108698355721</v>
+        <v>0.001746124634852797</v>
       </c>
       <c r="F127">
-        <v>0.7911607200704253</v>
+        <v>0.501747512419413</v>
       </c>
       <c r="G127">
-        <v>6.286845787247565E-07</v>
+        <v>1.255585692898019E-20</v>
       </c>
       <c r="H127">
-        <v>8.030282345486061E-07</v>
+        <v>1.257675282032032E-20</v>
       </c>
       <c r="I127">
-        <v>1.018647869688337E-06</v>
+        <v>1.259766452117807E-20</v>
       </c>
       <c r="J127">
-        <v>4.643737112291928E-07</v>
+        <v>1.193707889322363E-20</v>
       </c>
       <c r="K127">
-        <v>5.977988773959639E-07</v>
+        <v>1.195696393753636E-20</v>
       </c>
       <c r="L127">
-        <v>7.638494703298238E-07</v>
+        <v>1.197686403359755E-20</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5241,37 +5241,37 @@
         <v>126</v>
       </c>
       <c r="B128">
-        <v>1.962158185343565E-05</v>
+        <v>9.763015564006006E-21</v>
       </c>
       <c r="C128">
-        <v>1.551547526482338E-05</v>
+        <v>9.755258660330479E-21</v>
       </c>
       <c r="D128">
-        <v>0.790735190501814</v>
+        <v>0.9992054807631234</v>
       </c>
       <c r="E128">
-        <v>0.209264809498186</v>
+        <v>0.0007945192368765674</v>
       </c>
       <c r="F128">
-        <v>0.7560270373729719</v>
+        <v>0.5007947797840027</v>
       </c>
       <c r="G128">
-        <v>1.401306913907654E-07</v>
+        <v>2.088008675750428E-23</v>
       </c>
       <c r="H128">
-        <v>1.743436558238495E-07</v>
+        <v>2.089589134012695E-23</v>
       </c>
       <c r="I128">
-        <v>2.156196351397307E-07</v>
+        <v>2.091170085775498E-23</v>
       </c>
       <c r="J128">
-        <v>1.065444893769498E-07</v>
+        <v>1.986999726372171E-23</v>
       </c>
       <c r="K128">
-        <v>1.334251661667712E-07</v>
+        <v>1.988504431273633E-23</v>
       </c>
       <c r="L128">
-        <v>1.660505929338599E-07</v>
+        <v>1.990009606118625E-23</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5279,37 +5279,37 @@
         <v>127</v>
       </c>
       <c r="B129">
-        <v>4.106106588612276E-06</v>
+        <v>7.756903675528103E-24</v>
       </c>
       <c r="C129">
-        <v>3.33595148895662E-06</v>
+        <v>7.754360258289561E-24</v>
       </c>
       <c r="D129">
-        <v>0.8124366518415339</v>
+        <v>0.999672109214587</v>
       </c>
       <c r="E129">
-        <v>0.1875633481584661</v>
+        <v>0.0003278907854129542</v>
       </c>
       <c r="F129">
-        <v>0.7234595868599265</v>
+        <v>0.5003279305446376</v>
       </c>
       <c r="G129">
-        <v>2.819656003724771E-08</v>
+        <v>1.579964818713221E-26</v>
       </c>
       <c r="H129">
-        <v>3.421296443308413E-08</v>
+        <v>1.580458262267558E-26</v>
       </c>
       <c r="I129">
-        <v>4.127597931588113E-08</v>
+        <v>1.580951762801877E-26</v>
       </c>
       <c r="J129">
-        <v>2.202684502895224E-08</v>
+        <v>1.504235012197989E-26</v>
       </c>
       <c r="K129">
-        <v>2.68806767898214E-08</v>
+        <v>1.504704901462385E-26</v>
       </c>
       <c r="L129">
-        <v>3.26254267670887E-08</v>
+        <v>1.505174844991278E-26</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -5317,37 +5317,37 @@
         <v>128</v>
       </c>
       <c r="B130">
-        <v>7.701550996556558E-07</v>
+        <v>2.543417238541541E-27</v>
       </c>
       <c r="C130">
-        <v>6.416709452728503E-07</v>
+        <v>2.543108842288819E-27</v>
       </c>
       <c r="D130">
-        <v>0.8331710658797791</v>
+        <v>0.9998787472821807</v>
       </c>
       <c r="E130">
-        <v>0.1668289341202209</v>
+        <v>0.0001212527178192646</v>
       </c>
       <c r="F130">
-        <v>0.6913819467070551</v>
+        <v>0.5001212575236952</v>
       </c>
       <c r="G130">
-        <v>5.085231929939792E-09</v>
+        <v>4.933865765073465E-30</v>
       </c>
       <c r="H130">
-        <v>6.016404395836418E-09</v>
+        <v>4.934435543374224E-30</v>
       </c>
       <c r="I130">
-        <v>7.063014882797007E-09</v>
+        <v>4.935005343182054E-30</v>
       </c>
       <c r="J130">
-        <v>4.073911641647906E-09</v>
+        <v>4.698350019466757E-30</v>
       </c>
       <c r="K130">
-        <v>4.85383176086916E-09</v>
+        <v>4.698892643960407E-30</v>
       </c>
       <c r="L130">
-        <v>5.744749977267303E-09</v>
+        <v>4.699435288936982E-30</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -5355,37 +5355,37 @@
         <v>129</v>
       </c>
       <c r="B131">
-        <v>1.284841543828056E-07</v>
+        <v>3.083962527215307E-31</v>
       </c>
       <c r="C131">
-        <v>1.095745265271457E-07</v>
+        <v>3.083840293738347E-31</v>
       </c>
       <c r="D131">
-        <v>0.8528252145449737</v>
+        <v>0.9999603647982486</v>
       </c>
       <c r="E131">
-        <v>0.1471747854550263</v>
+        <v>3.96352017514312E-05</v>
       </c>
       <c r="F131">
-        <v>0.6471747854550263</v>
+        <v>0.5000396352017514</v>
       </c>
       <c r="G131">
-        <v>8.157344448326628E-10</v>
+        <v>5.697567936862695E-34</v>
       </c>
       <c r="H131">
-        <v>9.311724658966264E-10</v>
+        <v>5.697783007581429E-34</v>
       </c>
       <c r="I131">
-        <v>1.04661048696059E-09</v>
+        <v>5.697998078300163E-34</v>
       </c>
       <c r="J131">
-        <v>6.689220220443659E-10</v>
+        <v>5.426040107245738E-34</v>
       </c>
       <c r="K131">
-        <v>7.79920119221254E-10</v>
+        <v>5.426244936501675E-34</v>
       </c>
       <c r="L131">
-        <v>8.90918216398142E-10</v>
+        <v>5.426449765757611E-34</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -5393,10 +5393,10 @@
         <v>130</v>
       </c>
       <c r="B132">
-        <v>1.890962785565988E-08</v>
+        <v>1.222334769600324E-35</v>
       </c>
       <c r="C132">
-        <v>1.890962785565988E-08</v>
+        <v>1.222334769600324E-35</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -5408,22 +5408,22 @@
         <v>0.5</v>
       </c>
       <c r="G132">
-        <v>1.154380210639635E-10</v>
+        <v>2.150707187333701E-38</v>
       </c>
       <c r="H132">
-        <v>1.154380210639635E-10</v>
+        <v>2.150707187333701E-38</v>
       </c>
       <c r="I132">
-        <v>1.154380210639635E-10</v>
+        <v>2.150707187333701E-38</v>
       </c>
       <c r="J132">
-        <v>1.10998097176888E-10</v>
+        <v>2.048292559365429E-38</v>
       </c>
       <c r="K132">
-        <v>1.10998097176888E-10</v>
+        <v>2.048292559365429E-38</v>
       </c>
       <c r="L132">
-        <v>1.10998097176888E-10</v>
+        <v>2.048292559365429E-38</v>
       </c>
     </row>
   </sheetData>
